--- a/testFiles/SoilWaterContent.xlsx
+++ b/testFiles/SoilWaterContent.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="19126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bregaglio\Dropbox\IO\CREA\Progetti\AgriDigit\Pomodoro\TomGro_optimizer\Input files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://creagov-my.sharepoint.com/personal/simoneugomaria_bregaglio_crea_gov_it/Documents/Desktop/model dev/cumba/cumba_R_package/testFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{5A7756DC-657B-435E-BDEB-7295ED461E02}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="10_ncr:100000_{5A7756DC-657B-435E-BDEB-7295ED461E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D7A20A3-D1A4-427A-AC6A-32C9F6767538}"/>
   <bookViews>
-    <workbookView xWindow="576" yWindow="624" windowWidth="28164" windowHeight="12168" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -521,17 +521,8 @@
     <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="17" builtinId="30" customBuiltin="1"/>
@@ -590,10 +581,2253 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Foglio1!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SWC</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Foglio1!$E$2:$E$452</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="451"/>
+                <c:pt idx="0">
+                  <c:v>35.611257139999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>35.921441665000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>35.955710420000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>36.297966664999997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>38.684260414999997</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>36.439427080000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>36.229583335000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>36.082099999999997</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>36.033306249999995</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>36.006302085000002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>35.905041664999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>35.756874999999994</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>35.666428569999994</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>35.474166664999998</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>35.720641665000002</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>35.977812499999999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>36.006581249999996</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>36.310970834999999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>36.163297920000005</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>36.060622914999996</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>35.737793749999994</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>35.731041669999996</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>35.608939579999998</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>35.474635419999998</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>35.484843750000003</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>35.702608694999995</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>35.403993749999998</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>35.552831249999997</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>35.828870835000004</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>35.036043750000005</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>33.397154165000003</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>33.260552085</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33.975872914999997</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>32.736981249999999</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>32.757489585000002</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>33.673349999999999</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>33.329533335000001</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>32.118124999999999</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>31.873402079999998</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>33.464879164999999</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>31.909322914999997</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>32.123645835000005</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>33.558141669999998</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>32.262639579999998</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>30.907431250000002</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>31.199858335000002</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>33.22677083</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>33.192245649999997</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>33.070468750000003</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>32.841475000000003</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>32.907308335000003</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>31.423169565000002</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>31.694582610000001</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>33.21821739</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>33.222672914999997</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>33.153089585000004</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>33.338191664999997</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>33.502552080000001</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>32.255364580000006</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>32.318913039999998</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>32.630661764999999</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>32.640279164999995</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>32.660833330000003</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>32.693802085000002</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>32.822933335000002</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>30.980812499999999</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>30.704547914999999</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>31.704062499999999</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>30.985433335</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>31.045954164999998</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>29.488454165</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>30.165954165000002</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>29.1649125</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>27.621024999999999</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>26.620433335000001</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>27.325879999999998</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>26.688108334999999</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>26.258472914999999</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>26.600660415</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>25.89015625</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>25.30828125</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>25.138679170000003</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>25.019027080000001</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>24.744089580000001</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>24.411060419999998</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>24.093072915</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>23.810208334999999</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>23.598177085000003</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>23.42921875</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>23.28538125</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>23.179410415</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>23.098870830000003</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>23.049047914999999</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>23.02071042</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>23.000104165</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>35.661485714999998</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>35.740293749999999</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>35.678785415</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>36.316597915000003</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>39.67890208</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>37.685016669999996</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>37.246702084999995</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>36.993227079999997</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>36.821893750000001</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>36.748135415</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>36.724583335000005</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>36.673602944999999</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>36.618461539999998</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>36.514375000000001</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>37.117368749999997</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>37.322516664999995</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>37.45439167</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>37.426789580000005</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>37.047777080000003</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>36.825666665</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>36.661041664999999</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>36.674183330000005</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>36.477674999999998</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>36.358166664999999</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>36.734479164999996</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>37.082826085000001</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>36.564860420000002</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>37.147760419999997</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>37.484391665000004</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>36.79265625</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>35.5720125</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>36.903171740000005</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>37.368820835000001</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>35.979708329999994</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>36.202241665000003</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>37.053110414999999</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>36.489322915000002</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>34.814860414999998</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>35.155345835000006</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>38.165625000000006</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>36.392793749999996</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>36.449929170000004</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>38.504495835</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>37.675520829999996</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>35.865625000000001</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>35.602031249999996</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>37.106493749999998</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>38.405523909999999</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>38.067656249999999</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>38.097135414999997</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>37.843612499999999</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>35.665978260000003</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>35.101717395000001</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>36.000091304999998</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>36.723297915000003</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>35.931145834999995</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>36.550535414999999</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>36.878462499999998</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>35.234252085000001</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>36.337952170000001</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>36.452329415000001</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>37.194512500000002</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>37.015764584999999</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>37.150693750000002</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>36.580279165</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>34.399304165000004</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>35.5215125</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>37.076214585000002</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>37.761372914999995</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>37.664739580000003</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>38.682795835</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>38.140593750000001</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>36.503333330000004</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>35.173558334999996</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>37.059739585000003</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>38.397374999999997</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>36.938506250000003</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>37.489177085000001</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>38.456389584999997</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>37.091652080000003</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>37.197987499999996</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>38.318837500000001</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>37.428318750000003</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>36.472172915000002</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>35.359270835000004</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>33.79243125</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>31.9542875</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>30.140641670000001</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>28.4892</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>27.4386625</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>27.26095625</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>27.132764585</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>26.865450000000003</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>26.632708335</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>26.318662500000002</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>38.50486111</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>38.818835419999999</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>39.44848958</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>39.353785420000001</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>39.036958329999997</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>38.477743750000002</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>38.459166670000002</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>38.786354170000003</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>38.897760419999997</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>38.85430625</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>38.988595830000001</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>39.020106249999998</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>39.254056669999997</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>39.976428570000003</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>39.957935419999998</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>40.11982708</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>40.564877080000002</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>40.762519050000002</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>43.51267</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>42.44678571</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>42.061668179999998</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>43.051949999999998</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>42.944312500000002</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>42.098042499999998</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>41.074832499999999</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>42.163145450000002</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>42.523405259999997</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>41.309708819999997</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>42.363900000000001</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>42.374747370000001</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>41.289527499999998</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>40.452647059999997</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>39.440093179999998</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>38.287047919999999</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>40.241370830000001</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>42.390875000000001</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>40.893233330000001</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>40.177185420000001</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>39.774360420000001</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>39.32453125</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>40.977849999999997</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>41.562047919999998</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>40.709635419999998</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>40.6347375</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>39.867258329999999</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>39.152308329999997</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>40.21368125</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>41.11743542</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>41.85220417</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>41.557135420000002</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>40.712150000000001</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>40.261304170000003</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>42.044116670000001</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>42.699545829999998</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>43.446245830000002</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>43.049799999999998</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>43.39211667</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>43.11012083</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>41.735439579999998</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>42.299947920000001</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>42.471195829999999</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>42.804099999999998</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>42.653125000000003</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>43.447256250000002</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>43.08128542</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>42.131720829999999</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>41.4729375</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>41.00368125</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>41.661564579999997</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>41.894539469999998</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>42.49291667</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>42.72170208</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>41.770625000000003</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>42.263627079999999</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>42.627047920000003</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>41.705089579999999</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>40.992258329999999</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>40.239212500000001</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>39.422239580000003</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>38.547033329999998</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>37.558889579999999</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>36.151291669999999</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>34.342708330000001</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>32.055622919999998</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>30.649643749999999</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>30.015379169999999</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>29.389184090000001</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>40.650927777777774</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>41.047499999999985</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>41.69001875</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>41.609931249999995</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>41.40442083333334</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>40.656162500000001</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>40.577152083333331</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>40.905935416666672</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>41.059912500000003</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>41.17557291666666</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>41.375222916666665</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>41.464966666666669</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>41.778416666666665</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>42.770364285714287</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>42.708595833333334</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>42.831929166666662</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>42.881181250000004</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>42.724082499999994</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>43.692991666666671</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>43.788199999999996</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>43.690202380952378</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>43.930244736842099</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>44.136884999999999</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>43.441457499999991</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>41.309562499999991</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>40.59755454545455</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>41.987449999999995</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>39.344897058823534</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>41.283935</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>45.289013157894722</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>44.087687500000001</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>42.967155882352948</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>40.781477272727265</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>38.044947916666679</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>39.930695833333338</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>43.071042500000004</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>41.284220833333336</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>40.396162499999996</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>39.649014583333326</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>38.624235416666671</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>40.130850000000002</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>40.892031249999995</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>39.834895833333327</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>39.614008333333338</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>38.565970833333331</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>37.45817916666666</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>38.100518750000006</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>38.857658333333326</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>40.107954166666666</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>40.295762500000002</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>38.987212500000005</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>38.121416666666654</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>40.494114583333342</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>41.521456250000007</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>41.320939583333335</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>40.903390909090916</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>41.556806249999994</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>41.487068749999985</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>40.106562499999995</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>40.912622916666663</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>41.050587499999999</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>41.461433333333332</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>41.316927083333333</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>42.214706249999999</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>41.724706250000004</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>40.550508333333326</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>39.657872499999996</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>39.038333333333334</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>39.737516666666664</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>39.826684210526317</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>41.034704166666664</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>41.426093750000007</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>40.133804166666678</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>40.283127083333333</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>40.736441666666671</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>39.704927083333331</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>38.572920833333335</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>36.853506250000002</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>34.042012499999991</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>31.083460416666668</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>28.825729166666665</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>27.386275000000001</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>26.241041666666661</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>25.3863375</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>24.923489583333335</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>24.503662500000001</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>24.220284090909093</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>41.510972222222222</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>41.959254166666661</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>42.261266666666664</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>42.507412500000001</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>42.257554166666665</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>41.507310416666662</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>41.504774999999988</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>41.831006249999994</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>42.062902083333334</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>42.12088541666666</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>42.116454166666678</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>41.68831458333333</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>41.494635714285714</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>42.487021428571431</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>42.729029166666663</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>42.974843750000012</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>43.361562499999991</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>43.530752380952379</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>43.693214285714284</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>43.472710714285711</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>43.174980000000005</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>42.811390476190475</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>42.446414999999995</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>41.877272500000004</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>41.083562500000006</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>39.908275000000003</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>38.772549999999995</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>37.392376470588232</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>37.843442105263158</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>43.32203684210527</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>42.589812500000008</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>41.960541176470585</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>41.050815909090907</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>39.999235416666671</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>39.066231250000008</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>41.981517499999988</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>41.82480833333333</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>41.156995833333333</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>40.488139583333336</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>39.788574999999994</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>39.633997916666658</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>39.808925000000002</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>39.024985416666667</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>38.122287499999992</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>37.540831249999989</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>36.611650000000004</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>35.42160208333334</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>34.16530208333333</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>32.812879166666669</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>31.876722916666665</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>31.026891666666671</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>30.523733333333329</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>29.938385416666662</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>29.378872916666669</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>28.928956249999999</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>28.744836956521741</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>28.536372916666668</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>28.116564583333329</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>27.666866666666674</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>27.194014583333331</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>26.823718750000001</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>26.598405555555559</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>26.488768750000002</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>26.512947916666665</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>26.446662499999999</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>26.306608333333333</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>26.141222499999998</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>25.785920833333336</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>25.383822916666663</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>25.217963157894733</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>25.157114583333339</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>25.159252083333339</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>25.167777083333334</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>25.159293478260871</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>24.671093749999997</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>24.390345833333338</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>24.298504166666664</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>24.33663125</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>24.409877083333328</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>24.529449999999997</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>24.511927083333337</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>24.478690909090911</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>24.439062500000002</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>24.387152083333334</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>24.336649999999995</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>24.247795833333331</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>24.150681818181816</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-FB76-4889-B462-F608B9591672}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="250107871"/>
+        <c:axId val="250115551"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="250107871"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="250115551"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="250115551"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="250107871"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>316773</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>9253</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>113210</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>9253</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD61571F-1235-41D3-EE07-950B81AEEC72}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -631,9 +2865,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -666,26 +2900,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -718,26 +2935,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -912,12 +3112,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E452"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -934,7 +3134,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>27</v>
       </c>
@@ -951,7 +3151,7 @@
         <v>35.611257139999999</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>27</v>
       </c>
@@ -968,7 +3168,7 @@
         <v>35.921441665000003</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>27</v>
       </c>
@@ -985,7 +3185,7 @@
         <v>35.955710420000003</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>27</v>
       </c>
@@ -1002,7 +3202,7 @@
         <v>36.297966664999997</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>27</v>
       </c>
@@ -1019,7 +3219,7 @@
         <v>38.684260414999997</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>27</v>
       </c>
@@ -1036,7 +3236,7 @@
         <v>36.439427080000002</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>27</v>
       </c>
@@ -1053,7 +3253,7 @@
         <v>36.229583335000001</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>27</v>
       </c>
@@ -1070,7 +3270,7 @@
         <v>36.082099999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>27</v>
       </c>
@@ -1087,7 +3287,7 @@
         <v>36.033306249999995</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>27</v>
       </c>
@@ -1104,7 +3304,7 @@
         <v>36.006302085000002</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
         <v>27</v>
       </c>
@@ -1121,7 +3321,7 @@
         <v>35.905041664999999</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>27</v>
       </c>
@@ -1138,7 +3338,7 @@
         <v>35.756874999999994</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>27</v>
       </c>
@@ -1155,7 +3355,7 @@
         <v>35.666428569999994</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
         <v>27</v>
       </c>
@@ -1172,7 +3372,7 @@
         <v>35.474166664999998</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>27</v>
       </c>
@@ -1189,7 +3389,7 @@
         <v>35.720641665000002</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
         <v>27</v>
       </c>
@@ -1206,7 +3406,7 @@
         <v>35.977812499999999</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>27</v>
       </c>
@@ -1223,7 +3423,7 @@
         <v>36.006581249999996</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
         <v>27</v>
       </c>
@@ -1240,7 +3440,7 @@
         <v>36.310970834999999</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A20">
         <v>27</v>
       </c>
@@ -1257,7 +3457,7 @@
         <v>36.163297920000005</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A21">
         <v>27</v>
       </c>
@@ -1274,7 +3474,7 @@
         <v>36.060622914999996</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A22">
         <v>27</v>
       </c>
@@ -1291,7 +3491,7 @@
         <v>35.737793749999994</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
         <v>27</v>
       </c>
@@ -1308,7 +3508,7 @@
         <v>35.731041669999996</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
         <v>27</v>
       </c>
@@ -1325,7 +3525,7 @@
         <v>35.608939579999998</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
         <v>27</v>
       </c>
@@ -1342,7 +3542,7 @@
         <v>35.474635419999998</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A26">
         <v>27</v>
       </c>
@@ -1359,7 +3559,7 @@
         <v>35.484843750000003</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A27">
         <v>27</v>
       </c>
@@ -1376,7 +3576,7 @@
         <v>35.702608694999995</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1393,7 +3593,7 @@
         <v>35.403993749999998</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1410,7 +3610,7 @@
         <v>35.552831249999997</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A30">
         <v>27</v>
       </c>
@@ -1427,7 +3627,7 @@
         <v>35.828870835000004</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A31">
         <v>27</v>
       </c>
@@ -1444,7 +3644,7 @@
         <v>35.036043750000005</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A32">
         <v>27</v>
       </c>
@@ -1461,7 +3661,7 @@
         <v>33.397154165000003</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A33">
         <v>27</v>
       </c>
@@ -1478,7 +3678,7 @@
         <v>33.260552085</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A34">
         <v>27</v>
       </c>
@@ -1495,7 +3695,7 @@
         <v>33.975872914999997</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A35">
         <v>27</v>
       </c>
@@ -1512,7 +3712,7 @@
         <v>32.736981249999999</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A36">
         <v>27</v>
       </c>
@@ -1529,7 +3729,7 @@
         <v>32.757489585000002</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A37">
         <v>27</v>
       </c>
@@ -1546,7 +3746,7 @@
         <v>33.673349999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A38">
         <v>27</v>
       </c>
@@ -1563,7 +3763,7 @@
         <v>33.329533335000001</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A39">
         <v>27</v>
       </c>
@@ -1580,7 +3780,7 @@
         <v>32.118124999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A40">
         <v>27</v>
       </c>
@@ -1597,7 +3797,7 @@
         <v>31.873402079999998</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A41">
         <v>27</v>
       </c>
@@ -1614,7 +3814,7 @@
         <v>33.464879164999999</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A42">
         <v>27</v>
       </c>
@@ -1631,7 +3831,7 @@
         <v>31.909322914999997</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A43">
         <v>27</v>
       </c>
@@ -1648,7 +3848,7 @@
         <v>32.123645835000005</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A44">
         <v>27</v>
       </c>
@@ -1665,7 +3865,7 @@
         <v>33.558141669999998</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A45">
         <v>27</v>
       </c>
@@ -1682,7 +3882,7 @@
         <v>32.262639579999998</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A46">
         <v>27</v>
       </c>
@@ -1699,7 +3899,7 @@
         <v>30.907431250000002</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A47">
         <v>27</v>
       </c>
@@ -1716,7 +3916,7 @@
         <v>31.199858335000002</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A48">
         <v>27</v>
       </c>
@@ -1733,7 +3933,7 @@
         <v>33.22677083</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A49">
         <v>27</v>
       </c>
@@ -1750,7 +3950,7 @@
         <v>33.192245649999997</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A50">
         <v>27</v>
       </c>
@@ -1767,7 +3967,7 @@
         <v>33.070468750000003</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A51">
         <v>27</v>
       </c>
@@ -1784,7 +3984,7 @@
         <v>32.841475000000003</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A52">
         <v>27</v>
       </c>
@@ -1801,7 +4001,7 @@
         <v>32.907308335000003</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A53">
         <v>27</v>
       </c>
@@ -1818,7 +4018,7 @@
         <v>31.423169565000002</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A54">
         <v>27</v>
       </c>
@@ -1835,7 +4035,7 @@
         <v>31.694582610000001</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A55">
         <v>27</v>
       </c>
@@ -1852,7 +4052,7 @@
         <v>33.21821739</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A56">
         <v>27</v>
       </c>
@@ -1869,7 +4069,7 @@
         <v>33.222672914999997</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A57">
         <v>27</v>
       </c>
@@ -1886,7 +4086,7 @@
         <v>33.153089585000004</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A58">
         <v>27</v>
       </c>
@@ -1903,7 +4103,7 @@
         <v>33.338191664999997</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A59">
         <v>27</v>
       </c>
@@ -1920,7 +4120,7 @@
         <v>33.502552080000001</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A60">
         <v>27</v>
       </c>
@@ -1937,7 +4137,7 @@
         <v>32.255364580000006</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A61">
         <v>27</v>
       </c>
@@ -1954,7 +4154,7 @@
         <v>32.318913039999998</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A62">
         <v>27</v>
       </c>
@@ -1971,7 +4171,7 @@
         <v>32.630661764999999</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A63">
         <v>27</v>
       </c>
@@ -1988,7 +4188,7 @@
         <v>32.640279164999995</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A64">
         <v>27</v>
       </c>
@@ -2005,7 +4205,7 @@
         <v>32.660833330000003</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A65">
         <v>27</v>
       </c>
@@ -2022,7 +4222,7 @@
         <v>32.693802085000002</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A66">
         <v>27</v>
       </c>
@@ -2039,7 +4239,7 @@
         <v>32.822933335000002</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A67">
         <v>27</v>
       </c>
@@ -2056,7 +4256,7 @@
         <v>30.980812499999999</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A68">
         <v>27</v>
       </c>
@@ -2073,7 +4273,7 @@
         <v>30.704547914999999</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A69">
         <v>27</v>
       </c>
@@ -2090,7 +4290,7 @@
         <v>31.704062499999999</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A70">
         <v>27</v>
       </c>
@@ -2107,7 +4307,7 @@
         <v>30.985433335</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A71">
         <v>27</v>
       </c>
@@ -2124,7 +4324,7 @@
         <v>31.045954164999998</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A72">
         <v>27</v>
       </c>
@@ -2141,7 +4341,7 @@
         <v>29.488454165</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A73">
         <v>27</v>
       </c>
@@ -2158,7 +4358,7 @@
         <v>30.165954165000002</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A74">
         <v>27</v>
       </c>
@@ -2175,7 +4375,7 @@
         <v>29.1649125</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A75">
         <v>27</v>
       </c>
@@ -2192,7 +4392,7 @@
         <v>27.621024999999999</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A76">
         <v>27</v>
       </c>
@@ -2209,7 +4409,7 @@
         <v>26.620433335000001</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A77">
         <v>27</v>
       </c>
@@ -2226,7 +4426,7 @@
         <v>27.325879999999998</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A78">
         <v>27</v>
       </c>
@@ -2243,7 +4443,7 @@
         <v>26.688108334999999</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A79">
         <v>27</v>
       </c>
@@ -2260,7 +4460,7 @@
         <v>26.258472914999999</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A80">
         <v>27</v>
       </c>
@@ -2277,7 +4477,7 @@
         <v>26.600660415</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A81">
         <v>27</v>
       </c>
@@ -2294,7 +4494,7 @@
         <v>25.89015625</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A82">
         <v>27</v>
       </c>
@@ -2311,7 +4511,7 @@
         <v>25.30828125</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A83">
         <v>27</v>
       </c>
@@ -2328,7 +4528,7 @@
         <v>25.138679170000003</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A84">
         <v>27</v>
       </c>
@@ -2345,7 +4545,7 @@
         <v>25.019027080000001</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A85">
         <v>27</v>
       </c>
@@ -2362,7 +4562,7 @@
         <v>24.744089580000001</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A86">
         <v>27</v>
       </c>
@@ -2379,7 +4579,7 @@
         <v>24.411060419999998</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A87">
         <v>27</v>
       </c>
@@ -2396,7 +4596,7 @@
         <v>24.093072915</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A88">
         <v>27</v>
       </c>
@@ -2413,7 +4613,7 @@
         <v>23.810208334999999</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A89">
         <v>27</v>
       </c>
@@ -2430,7 +4630,7 @@
         <v>23.598177085000003</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A90">
         <v>27</v>
       </c>
@@ -2447,7 +4647,7 @@
         <v>23.42921875</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A91">
         <v>27</v>
       </c>
@@ -2464,7 +4664,7 @@
         <v>23.28538125</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A92">
         <v>27</v>
       </c>
@@ -2481,7 +4681,7 @@
         <v>23.179410415</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A93">
         <v>27</v>
       </c>
@@ -2498,7 +4698,7 @@
         <v>23.098870830000003</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A94">
         <v>27</v>
       </c>
@@ -2515,7 +4715,7 @@
         <v>23.049047914999999</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A95">
         <v>27</v>
       </c>
@@ -2532,7 +4732,7 @@
         <v>23.02071042</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A96">
         <v>27</v>
       </c>
@@ -2549,7 +4749,7 @@
         <v>23.000104165</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A97">
         <v>28</v>
       </c>
@@ -2566,7 +4766,7 @@
         <v>35.661485714999998</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A98">
         <v>28</v>
       </c>
@@ -2583,7 +4783,7 @@
         <v>35.740293749999999</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A99">
         <v>28</v>
       </c>
@@ -2600,7 +4800,7 @@
         <v>35.678785415</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A100">
         <v>28</v>
       </c>
@@ -2617,7 +4817,7 @@
         <v>36.316597915000003</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A101">
         <v>28</v>
       </c>
@@ -2634,7 +4834,7 @@
         <v>39.67890208</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A102">
         <v>28</v>
       </c>
@@ -2651,7 +4851,7 @@
         <v>37.685016669999996</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A103">
         <v>28</v>
       </c>
@@ -2668,7 +4868,7 @@
         <v>37.246702084999995</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A104">
         <v>28</v>
       </c>
@@ -2685,7 +4885,7 @@
         <v>36.993227079999997</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A105">
         <v>28</v>
       </c>
@@ -2702,7 +4902,7 @@
         <v>36.821893750000001</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A106">
         <v>28</v>
       </c>
@@ -2719,7 +4919,7 @@
         <v>36.748135415</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A107">
         <v>28</v>
       </c>
@@ -2736,7 +4936,7 @@
         <v>36.724583335000005</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A108">
         <v>28</v>
       </c>
@@ -2753,7 +4953,7 @@
         <v>36.673602944999999</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A109">
         <v>28</v>
       </c>
@@ -2770,7 +4970,7 @@
         <v>36.618461539999998</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A110">
         <v>28</v>
       </c>
@@ -2787,7 +4987,7 @@
         <v>36.514375000000001</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A111">
         <v>28</v>
       </c>
@@ -2804,7 +5004,7 @@
         <v>37.117368749999997</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A112">
         <v>28</v>
       </c>
@@ -2821,7 +5021,7 @@
         <v>37.322516664999995</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A113">
         <v>28</v>
       </c>
@@ -2838,7 +5038,7 @@
         <v>37.45439167</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A114">
         <v>28</v>
       </c>
@@ -2855,7 +5055,7 @@
         <v>37.426789580000005</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A115">
         <v>28</v>
       </c>
@@ -2872,7 +5072,7 @@
         <v>37.047777080000003</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A116">
         <v>28</v>
       </c>
@@ -2889,7 +5089,7 @@
         <v>36.825666665</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A117">
         <v>28</v>
       </c>
@@ -2906,7 +5106,7 @@
         <v>36.661041664999999</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A118">
         <v>28</v>
       </c>
@@ -2923,7 +5123,7 @@
         <v>36.674183330000005</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A119">
         <v>28</v>
       </c>
@@ -2940,7 +5140,7 @@
         <v>36.477674999999998</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A120">
         <v>28</v>
       </c>
@@ -2957,7 +5157,7 @@
         <v>36.358166664999999</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A121">
         <v>28</v>
       </c>
@@ -2974,7 +5174,7 @@
         <v>36.734479164999996</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A122">
         <v>28</v>
       </c>
@@ -2991,7 +5191,7 @@
         <v>37.082826085000001</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A123">
         <v>28</v>
       </c>
@@ -3008,7 +5208,7 @@
         <v>36.564860420000002</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A124">
         <v>28</v>
       </c>
@@ -3025,7 +5225,7 @@
         <v>37.147760419999997</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A125">
         <v>28</v>
       </c>
@@ -3042,7 +5242,7 @@
         <v>37.484391665000004</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A126">
         <v>28</v>
       </c>
@@ -3059,7 +5259,7 @@
         <v>36.79265625</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A127">
         <v>28</v>
       </c>
@@ -3076,7 +5276,7 @@
         <v>35.5720125</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A128">
         <v>28</v>
       </c>
@@ -3093,7 +5293,7 @@
         <v>36.903171740000005</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A129">
         <v>28</v>
       </c>
@@ -3110,7 +5310,7 @@
         <v>37.368820835000001</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A130">
         <v>28</v>
       </c>
@@ -3127,7 +5327,7 @@
         <v>35.979708329999994</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A131">
         <v>28</v>
       </c>
@@ -3144,7 +5344,7 @@
         <v>36.202241665000003</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A132">
         <v>28</v>
       </c>
@@ -3161,7 +5361,7 @@
         <v>37.053110414999999</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A133">
         <v>28</v>
       </c>
@@ -3178,7 +5378,7 @@
         <v>36.489322915000002</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A134">
         <v>28</v>
       </c>
@@ -3195,7 +5395,7 @@
         <v>34.814860414999998</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A135">
         <v>28</v>
       </c>
@@ -3212,7 +5412,7 @@
         <v>35.155345835000006</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A136">
         <v>28</v>
       </c>
@@ -3229,7 +5429,7 @@
         <v>38.165625000000006</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A137">
         <v>28</v>
       </c>
@@ -3246,7 +5446,7 @@
         <v>36.392793749999996</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A138">
         <v>28</v>
       </c>
@@ -3263,7 +5463,7 @@
         <v>36.449929170000004</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A139">
         <v>28</v>
       </c>
@@ -3280,7 +5480,7 @@
         <v>38.504495835</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A140">
         <v>28</v>
       </c>
@@ -3297,7 +5497,7 @@
         <v>37.675520829999996</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A141">
         <v>28</v>
       </c>
@@ -3314,7 +5514,7 @@
         <v>35.865625000000001</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A142">
         <v>28</v>
       </c>
@@ -3331,7 +5531,7 @@
         <v>35.602031249999996</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A143">
         <v>28</v>
       </c>
@@ -3348,7 +5548,7 @@
         <v>37.106493749999998</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A144">
         <v>28</v>
       </c>
@@ -3365,7 +5565,7 @@
         <v>38.405523909999999</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A145">
         <v>28</v>
       </c>
@@ -3382,7 +5582,7 @@
         <v>38.067656249999999</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A146">
         <v>28</v>
       </c>
@@ -3399,7 +5599,7 @@
         <v>38.097135414999997</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A147">
         <v>28</v>
       </c>
@@ -3416,7 +5616,7 @@
         <v>37.843612499999999</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A148">
         <v>28</v>
       </c>
@@ -3433,7 +5633,7 @@
         <v>35.665978260000003</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A149">
         <v>28</v>
       </c>
@@ -3450,7 +5650,7 @@
         <v>35.101717395000001</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A150">
         <v>28</v>
       </c>
@@ -3467,7 +5667,7 @@
         <v>36.000091304999998</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A151">
         <v>28</v>
       </c>
@@ -3484,7 +5684,7 @@
         <v>36.723297915000003</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A152">
         <v>28</v>
       </c>
@@ -3501,7 +5701,7 @@
         <v>35.931145834999995</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A153">
         <v>28</v>
       </c>
@@ -3518,7 +5718,7 @@
         <v>36.550535414999999</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A154">
         <v>28</v>
       </c>
@@ -3535,7 +5735,7 @@
         <v>36.878462499999998</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A155">
         <v>28</v>
       </c>
@@ -3552,7 +5752,7 @@
         <v>35.234252085000001</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A156">
         <v>28</v>
       </c>
@@ -3569,7 +5769,7 @@
         <v>36.337952170000001</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A157">
         <v>28</v>
       </c>
@@ -3586,7 +5786,7 @@
         <v>36.452329415000001</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A158">
         <v>28</v>
       </c>
@@ -3603,7 +5803,7 @@
         <v>37.194512500000002</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A159">
         <v>28</v>
       </c>
@@ -3620,7 +5820,7 @@
         <v>37.015764584999999</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A160">
         <v>28</v>
       </c>
@@ -3637,7 +5837,7 @@
         <v>37.150693750000002</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A161">
         <v>28</v>
       </c>
@@ -3654,7 +5854,7 @@
         <v>36.580279165</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A162">
         <v>28</v>
       </c>
@@ -3671,7 +5871,7 @@
         <v>34.399304165000004</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A163">
         <v>28</v>
       </c>
@@ -3688,7 +5888,7 @@
         <v>35.5215125</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A164">
         <v>28</v>
       </c>
@@ -3705,7 +5905,7 @@
         <v>37.076214585000002</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A165">
         <v>28</v>
       </c>
@@ -3722,7 +5922,7 @@
         <v>37.761372914999995</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A166">
         <v>28</v>
       </c>
@@ -3739,7 +5939,7 @@
         <v>37.664739580000003</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A167">
         <v>28</v>
       </c>
@@ -3756,7 +5956,7 @@
         <v>38.682795835</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A168">
         <v>28</v>
       </c>
@@ -3773,7 +5973,7 @@
         <v>38.140593750000001</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A169">
         <v>28</v>
       </c>
@@ -3790,7 +5990,7 @@
         <v>36.503333330000004</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A170">
         <v>28</v>
       </c>
@@ -3807,7 +6007,7 @@
         <v>35.173558334999996</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A171">
         <v>28</v>
       </c>
@@ -3824,7 +6024,7 @@
         <v>37.059739585000003</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A172">
         <v>28</v>
       </c>
@@ -3841,7 +6041,7 @@
         <v>38.397374999999997</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A173">
         <v>28</v>
       </c>
@@ -3858,7 +6058,7 @@
         <v>36.938506250000003</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A174">
         <v>28</v>
       </c>
@@ -3875,7 +6075,7 @@
         <v>37.489177085000001</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A175">
         <v>28</v>
       </c>
@@ -3892,7 +6092,7 @@
         <v>38.456389584999997</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A176">
         <v>28</v>
       </c>
@@ -3909,7 +6109,7 @@
         <v>37.091652080000003</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A177">
         <v>28</v>
       </c>
@@ -3926,7 +6126,7 @@
         <v>37.197987499999996</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A178">
         <v>28</v>
       </c>
@@ -3943,7 +6143,7 @@
         <v>38.318837500000001</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A179">
         <v>28</v>
       </c>
@@ -3960,7 +6160,7 @@
         <v>37.428318750000003</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A180">
         <v>28</v>
       </c>
@@ -3977,7 +6177,7 @@
         <v>36.472172915000002</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A181">
         <v>28</v>
       </c>
@@ -3994,7 +6194,7 @@
         <v>35.359270835000004</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A182">
         <v>28</v>
       </c>
@@ -4011,7 +6211,7 @@
         <v>33.79243125</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A183">
         <v>28</v>
       </c>
@@ -4028,7 +6228,7 @@
         <v>31.9542875</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A184">
         <v>28</v>
       </c>
@@ -4045,7 +6245,7 @@
         <v>30.140641670000001</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A185">
         <v>28</v>
       </c>
@@ -4062,7 +6262,7 @@
         <v>28.4892</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A186">
         <v>28</v>
       </c>
@@ -4079,7 +6279,7 @@
         <v>27.4386625</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A187">
         <v>28</v>
       </c>
@@ -4096,7 +6296,7 @@
         <v>27.26095625</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A188">
         <v>28</v>
       </c>
@@ -4113,7 +6313,7 @@
         <v>27.132764585</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A189">
         <v>28</v>
       </c>
@@ -4130,7 +6330,7 @@
         <v>26.865450000000003</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A190">
         <v>28</v>
       </c>
@@ -4147,7 +6347,7 @@
         <v>26.632708335</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A191">
         <v>28</v>
       </c>
@@ -4164,7 +6364,7 @@
         <v>26.318662500000002</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A192">
         <v>32</v>
       </c>
@@ -4181,7 +6381,7 @@
         <v>38.50486111</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A193">
         <v>32</v>
       </c>
@@ -4198,7 +6398,7 @@
         <v>38.818835419999999</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A194">
         <v>32</v>
       </c>
@@ -4215,7 +6415,7 @@
         <v>39.44848958</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A195">
         <v>32</v>
       </c>
@@ -4232,7 +6432,7 @@
         <v>39.353785420000001</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A196">
         <v>32</v>
       </c>
@@ -4249,7 +6449,7 @@
         <v>39.036958329999997</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A197">
         <v>32</v>
       </c>
@@ -4266,7 +6466,7 @@
         <v>38.477743750000002</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A198">
         <v>32</v>
       </c>
@@ -4283,7 +6483,7 @@
         <v>38.459166670000002</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A199">
         <v>32</v>
       </c>
@@ -4300,7 +6500,7 @@
         <v>38.786354170000003</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A200">
         <v>32</v>
       </c>
@@ -4317,7 +6517,7 @@
         <v>38.897760419999997</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A201">
         <v>32</v>
       </c>
@@ -4334,7 +6534,7 @@
         <v>38.85430625</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A202">
         <v>32</v>
       </c>
@@ -4351,7 +6551,7 @@
         <v>38.988595830000001</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A203">
         <v>32</v>
       </c>
@@ -4368,7 +6568,7 @@
         <v>39.020106249999998</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A204">
         <v>32</v>
       </c>
@@ -4385,7 +6585,7 @@
         <v>39.254056669999997</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A205">
         <v>32</v>
       </c>
@@ -4402,7 +6602,7 @@
         <v>39.976428570000003</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A206">
         <v>32</v>
       </c>
@@ -4419,7 +6619,7 @@
         <v>39.957935419999998</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A207">
         <v>32</v>
       </c>
@@ -4436,7 +6636,7 @@
         <v>40.11982708</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A208">
         <v>32</v>
       </c>
@@ -4453,7 +6653,7 @@
         <v>40.564877080000002</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A209">
         <v>32</v>
       </c>
@@ -4470,7 +6670,7 @@
         <v>40.762519050000002</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A210">
         <v>32</v>
       </c>
@@ -4487,7 +6687,7 @@
         <v>43.51267</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A211">
         <v>32</v>
       </c>
@@ -4504,7 +6704,7 @@
         <v>42.44678571</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A212">
         <v>32</v>
       </c>
@@ -4521,7 +6721,7 @@
         <v>42.061668179999998</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A213">
         <v>32</v>
       </c>
@@ -4538,7 +6738,7 @@
         <v>43.051949999999998</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A214">
         <v>32</v>
       </c>
@@ -4555,7 +6755,7 @@
         <v>42.944312500000002</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A215">
         <v>32</v>
       </c>
@@ -4572,7 +6772,7 @@
         <v>42.098042499999998</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A216">
         <v>32</v>
       </c>
@@ -4589,7 +6789,7 @@
         <v>41.074832499999999</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A217">
         <v>32</v>
       </c>
@@ -4606,7 +6806,7 @@
         <v>42.163145450000002</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A218">
         <v>32</v>
       </c>
@@ -4623,7 +6823,7 @@
         <v>42.523405259999997</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A219">
         <v>32</v>
       </c>
@@ -4640,7 +6840,7 @@
         <v>41.309708819999997</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A220">
         <v>32</v>
       </c>
@@ -4657,7 +6857,7 @@
         <v>42.363900000000001</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A221">
         <v>32</v>
       </c>
@@ -4674,7 +6874,7 @@
         <v>42.374747370000001</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A222">
         <v>32</v>
       </c>
@@ -4691,7 +6891,7 @@
         <v>41.289527499999998</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A223">
         <v>32</v>
       </c>
@@ -4708,7 +6908,7 @@
         <v>40.452647059999997</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A224">
         <v>32</v>
       </c>
@@ -4725,7 +6925,7 @@
         <v>39.440093179999998</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A225">
         <v>32</v>
       </c>
@@ -4742,7 +6942,7 @@
         <v>38.287047919999999</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A226">
         <v>32</v>
       </c>
@@ -4759,7 +6959,7 @@
         <v>40.241370830000001</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A227">
         <v>32</v>
       </c>
@@ -4776,7 +6976,7 @@
         <v>42.390875000000001</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A228">
         <v>32</v>
       </c>
@@ -4793,7 +6993,7 @@
         <v>40.893233330000001</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A229">
         <v>32</v>
       </c>
@@ -4810,7 +7010,7 @@
         <v>40.177185420000001</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A230">
         <v>32</v>
       </c>
@@ -4827,7 +7027,7 @@
         <v>39.774360420000001</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A231">
         <v>32</v>
       </c>
@@ -4844,7 +7044,7 @@
         <v>39.32453125</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A232">
         <v>32</v>
       </c>
@@ -4861,7 +7061,7 @@
         <v>40.977849999999997</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A233">
         <v>32</v>
       </c>
@@ -4878,7 +7078,7 @@
         <v>41.562047919999998</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A234">
         <v>32</v>
       </c>
@@ -4895,7 +7095,7 @@
         <v>40.709635419999998</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A235">
         <v>32</v>
       </c>
@@ -4912,7 +7112,7 @@
         <v>40.6347375</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A236">
         <v>32</v>
       </c>
@@ -4929,7 +7129,7 @@
         <v>39.867258329999999</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A237">
         <v>32</v>
       </c>
@@ -4946,7 +7146,7 @@
         <v>39.152308329999997</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A238">
         <v>32</v>
       </c>
@@ -4963,7 +7163,7 @@
         <v>40.21368125</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A239">
         <v>32</v>
       </c>
@@ -4980,7 +7180,7 @@
         <v>41.11743542</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A240">
         <v>32</v>
       </c>
@@ -4997,7 +7197,7 @@
         <v>41.85220417</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A241">
         <v>32</v>
       </c>
@@ -5014,7 +7214,7 @@
         <v>41.557135420000002</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A242">
         <v>32</v>
       </c>
@@ -5031,7 +7231,7 @@
         <v>40.712150000000001</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A243">
         <v>32</v>
       </c>
@@ -5048,7 +7248,7 @@
         <v>40.261304170000003</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A244">
         <v>32</v>
       </c>
@@ -5065,7 +7265,7 @@
         <v>42.044116670000001</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A245">
         <v>32</v>
       </c>
@@ -5082,7 +7282,7 @@
         <v>42.699545829999998</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A246">
         <v>32</v>
       </c>
@@ -5099,7 +7299,7 @@
         <v>43.446245830000002</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A247">
         <v>32</v>
       </c>
@@ -5116,7 +7316,7 @@
         <v>43.049799999999998</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A248">
         <v>32</v>
       </c>
@@ -5133,7 +7333,7 @@
         <v>43.39211667</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A249">
         <v>32</v>
       </c>
@@ -5150,7 +7350,7 @@
         <v>43.11012083</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A250">
         <v>32</v>
       </c>
@@ -5167,7 +7367,7 @@
         <v>41.735439579999998</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A251">
         <v>32</v>
       </c>
@@ -5184,7 +7384,7 @@
         <v>42.299947920000001</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A252">
         <v>32</v>
       </c>
@@ -5201,7 +7401,7 @@
         <v>42.471195829999999</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A253">
         <v>32</v>
       </c>
@@ -5218,7 +7418,7 @@
         <v>42.804099999999998</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A254">
         <v>32</v>
       </c>
@@ -5235,7 +7435,7 @@
         <v>42.653125000000003</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A255">
         <v>32</v>
       </c>
@@ -5252,7 +7452,7 @@
         <v>43.447256250000002</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A256">
         <v>32</v>
       </c>
@@ -5269,7 +7469,7 @@
         <v>43.08128542</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A257">
         <v>32</v>
       </c>
@@ -5286,7 +7486,7 @@
         <v>42.131720829999999</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A258">
         <v>32</v>
       </c>
@@ -5303,7 +7503,7 @@
         <v>41.4729375</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A259">
         <v>32</v>
       </c>
@@ -5320,7 +7520,7 @@
         <v>41.00368125</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A260">
         <v>32</v>
       </c>
@@ -5337,7 +7537,7 @@
         <v>41.661564579999997</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A261">
         <v>32</v>
       </c>
@@ -5354,7 +7554,7 @@
         <v>41.894539469999998</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A262">
         <v>32</v>
       </c>
@@ -5371,7 +7571,7 @@
         <v>42.49291667</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A263">
         <v>32</v>
       </c>
@@ -5388,7 +7588,7 @@
         <v>42.72170208</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A264">
         <v>32</v>
       </c>
@@ -5405,7 +7605,7 @@
         <v>41.770625000000003</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A265">
         <v>32</v>
       </c>
@@ -5422,7 +7622,7 @@
         <v>42.263627079999999</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A266">
         <v>32</v>
       </c>
@@ -5439,7 +7639,7 @@
         <v>42.627047920000003</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A267">
         <v>32</v>
       </c>
@@ -5456,7 +7656,7 @@
         <v>41.705089579999999</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A268">
         <v>32</v>
       </c>
@@ -5473,7 +7673,7 @@
         <v>40.992258329999999</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A269">
         <v>32</v>
       </c>
@@ -5490,7 +7690,7 @@
         <v>40.239212500000001</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A270">
         <v>32</v>
       </c>
@@ -5507,7 +7707,7 @@
         <v>39.422239580000003</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A271">
         <v>32</v>
       </c>
@@ -5524,7 +7724,7 @@
         <v>38.547033329999998</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A272">
         <v>32</v>
       </c>
@@ -5541,7 +7741,7 @@
         <v>37.558889579999999</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A273">
         <v>32</v>
       </c>
@@ -5558,7 +7758,7 @@
         <v>36.151291669999999</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A274">
         <v>32</v>
       </c>
@@ -5575,7 +7775,7 @@
         <v>34.342708330000001</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A275">
         <v>32</v>
       </c>
@@ -5592,7 +7792,7 @@
         <v>32.055622919999998</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A276">
         <v>32</v>
       </c>
@@ -5609,7 +7809,7 @@
         <v>30.649643749999999</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A277">
         <v>32</v>
       </c>
@@ -5626,7 +7826,7 @@
         <v>30.015379169999999</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A278">
         <v>32</v>
       </c>
@@ -5643,7 +7843,7 @@
         <v>29.389184090000001</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A279">
         <v>30</v>
       </c>
@@ -5656,12 +7856,12 @@
       <c r="D279">
         <v>11</v>
       </c>
-      <c r="E279" s="1">
+      <c r="E279">
         <v>40.650927777777774</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A280" s="4">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A280">
         <v>30</v>
       </c>
       <c r="B280">
@@ -5673,12 +7873,12 @@
       <c r="D280">
         <v>12</v>
       </c>
-      <c r="E280" s="1">
+      <c r="E280">
         <v>41.047499999999985</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A281" s="4">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A281">
         <v>30</v>
       </c>
       <c r="B281">
@@ -5690,12 +7890,12 @@
       <c r="D281">
         <v>13</v>
       </c>
-      <c r="E281" s="1">
+      <c r="E281">
         <v>41.69001875</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A282" s="4">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A282">
         <v>30</v>
       </c>
       <c r="B282">
@@ -5707,12 +7907,12 @@
       <c r="D282">
         <v>14</v>
       </c>
-      <c r="E282" s="1">
+      <c r="E282">
         <v>41.609931249999995</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A283" s="4">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A283">
         <v>30</v>
       </c>
       <c r="B283">
@@ -5724,12 +7924,12 @@
       <c r="D283">
         <v>15</v>
       </c>
-      <c r="E283" s="1">
+      <c r="E283">
         <v>41.40442083333334</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A284" s="4">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A284">
         <v>30</v>
       </c>
       <c r="B284">
@@ -5741,12 +7941,12 @@
       <c r="D284">
         <v>16</v>
       </c>
-      <c r="E284" s="1">
+      <c r="E284">
         <v>40.656162500000001</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A285" s="4">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A285">
         <v>30</v>
       </c>
       <c r="B285">
@@ -5758,12 +7958,12 @@
       <c r="D285">
         <v>17</v>
       </c>
-      <c r="E285" s="1">
+      <c r="E285">
         <v>40.577152083333331</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A286" s="4">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A286">
         <v>30</v>
       </c>
       <c r="B286">
@@ -5775,12 +7975,12 @@
       <c r="D286">
         <v>18</v>
       </c>
-      <c r="E286" s="1">
+      <c r="E286">
         <v>40.905935416666672</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A287" s="4">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A287">
         <v>30</v>
       </c>
       <c r="B287">
@@ -5792,12 +7992,12 @@
       <c r="D287">
         <v>19</v>
       </c>
-      <c r="E287" s="1">
+      <c r="E287">
         <v>41.059912500000003</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A288" s="4">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A288">
         <v>30</v>
       </c>
       <c r="B288">
@@ -5809,12 +8009,12 @@
       <c r="D288">
         <v>20</v>
       </c>
-      <c r="E288" s="1">
+      <c r="E288">
         <v>41.17557291666666</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A289" s="4">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A289">
         <v>30</v>
       </c>
       <c r="B289">
@@ -5826,12 +8026,12 @@
       <c r="D289">
         <v>21</v>
       </c>
-      <c r="E289" s="1">
+      <c r="E289">
         <v>41.375222916666665</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A290" s="4">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A290">
         <v>30</v>
       </c>
       <c r="B290">
@@ -5843,12 +8043,12 @@
       <c r="D290">
         <v>22</v>
       </c>
-      <c r="E290" s="1">
+      <c r="E290">
         <v>41.464966666666669</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A291" s="4">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A291">
         <v>30</v>
       </c>
       <c r="B291">
@@ -5860,12 +8060,12 @@
       <c r="D291">
         <v>23</v>
       </c>
-      <c r="E291" s="1">
+      <c r="E291">
         <v>41.778416666666665</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A292" s="4">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A292">
         <v>30</v>
       </c>
       <c r="B292">
@@ -5877,12 +8077,12 @@
       <c r="D292">
         <v>24</v>
       </c>
-      <c r="E292" s="1">
+      <c r="E292">
         <v>42.770364285714287</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A293" s="4">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A293">
         <v>30</v>
       </c>
       <c r="B293">
@@ -5894,12 +8094,12 @@
       <c r="D293">
         <v>25</v>
       </c>
-      <c r="E293" s="1">
+      <c r="E293">
         <v>42.708595833333334</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A294" s="4">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A294">
         <v>30</v>
       </c>
       <c r="B294">
@@ -5911,12 +8111,12 @@
       <c r="D294">
         <v>26</v>
       </c>
-      <c r="E294" s="1">
+      <c r="E294">
         <v>42.831929166666662</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A295" s="4">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A295">
         <v>30</v>
       </c>
       <c r="B295">
@@ -5928,12 +8128,12 @@
       <c r="D295">
         <v>27</v>
       </c>
-      <c r="E295" s="1">
+      <c r="E295">
         <v>42.881181250000004</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A296" s="4">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A296">
         <v>30</v>
       </c>
       <c r="B296">
@@ -5945,12 +8145,12 @@
       <c r="D296">
         <v>28</v>
       </c>
-      <c r="E296" s="1">
+      <c r="E296">
         <v>42.724082499999994</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A297" s="4">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A297">
         <v>30</v>
       </c>
       <c r="B297">
@@ -5962,12 +8162,12 @@
       <c r="D297">
         <v>29</v>
       </c>
-      <c r="E297" s="1">
+      <c r="E297">
         <v>43.692991666666671</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A298" s="4">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A298">
         <v>30</v>
       </c>
       <c r="B298">
@@ -5979,12 +8179,12 @@
       <c r="D298">
         <v>30</v>
       </c>
-      <c r="E298" s="1">
+      <c r="E298">
         <v>43.788199999999996</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A299" s="4">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A299">
         <v>30</v>
       </c>
       <c r="B299">
@@ -5996,12 +8196,12 @@
       <c r="D299">
         <v>31</v>
       </c>
-      <c r="E299" s="1">
+      <c r="E299">
         <v>43.690202380952378</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A300" s="4">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A300">
         <v>30</v>
       </c>
       <c r="B300">
@@ -6013,12 +8213,12 @@
       <c r="D300">
         <v>1</v>
       </c>
-      <c r="E300" s="2">
+      <c r="E300">
         <v>43.930244736842099</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A301" s="4">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A301">
         <v>30</v>
       </c>
       <c r="B301">
@@ -6030,12 +8230,12 @@
       <c r="D301">
         <v>2</v>
       </c>
-      <c r="E301" s="2">
+      <c r="E301">
         <v>44.136884999999999</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A302" s="4">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A302">
         <v>30</v>
       </c>
       <c r="B302">
@@ -6047,12 +8247,12 @@
       <c r="D302">
         <v>3</v>
       </c>
-      <c r="E302" s="2">
+      <c r="E302">
         <v>43.441457499999991</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A303" s="4">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A303">
         <v>30</v>
       </c>
       <c r="B303">
@@ -6064,12 +8264,12 @@
       <c r="D303">
         <v>4</v>
       </c>
-      <c r="E303" s="2">
+      <c r="E303">
         <v>41.309562499999991</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A304" s="4">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A304">
         <v>30</v>
       </c>
       <c r="B304">
@@ -6081,12 +8281,12 @@
       <c r="D304">
         <v>5</v>
       </c>
-      <c r="E304" s="2">
+      <c r="E304">
         <v>40.59755454545455</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A305" s="4">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A305">
         <v>30</v>
       </c>
       <c r="B305">
@@ -6098,12 +8298,12 @@
       <c r="D305">
         <v>6</v>
       </c>
-      <c r="E305" s="2">
+      <c r="E305">
         <v>41.987449999999995</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A306" s="4">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A306">
         <v>30</v>
       </c>
       <c r="B306">
@@ -6115,12 +8315,12 @@
       <c r="D306">
         <v>7</v>
       </c>
-      <c r="E306" s="2">
+      <c r="E306">
         <v>39.344897058823534</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A307" s="4">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A307">
         <v>30</v>
       </c>
       <c r="B307">
@@ -6132,12 +8332,12 @@
       <c r="D307">
         <v>8</v>
       </c>
-      <c r="E307" s="2">
+      <c r="E307">
         <v>41.283935</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A308" s="4">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A308">
         <v>30</v>
       </c>
       <c r="B308">
@@ -6149,12 +8349,12 @@
       <c r="D308">
         <v>9</v>
       </c>
-      <c r="E308" s="2">
+      <c r="E308">
         <v>45.289013157894722</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A309" s="4">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A309">
         <v>30</v>
       </c>
       <c r="B309">
@@ -6166,12 +8366,12 @@
       <c r="D309">
         <v>10</v>
       </c>
-      <c r="E309" s="2">
+      <c r="E309">
         <v>44.087687500000001</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A310" s="4">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A310">
         <v>30</v>
       </c>
       <c r="B310">
@@ -6183,12 +8383,12 @@
       <c r="D310">
         <v>11</v>
       </c>
-      <c r="E310" s="2">
+      <c r="E310">
         <v>42.967155882352948</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A311" s="4">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A311">
         <v>30</v>
       </c>
       <c r="B311">
@@ -6200,12 +8400,12 @@
       <c r="D311">
         <v>12</v>
       </c>
-      <c r="E311" s="2">
+      <c r="E311">
         <v>40.781477272727265</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A312" s="4">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A312">
         <v>30</v>
       </c>
       <c r="B312">
@@ -6217,12 +8417,12 @@
       <c r="D312">
         <v>13</v>
       </c>
-      <c r="E312" s="2">
+      <c r="E312">
         <v>38.044947916666679</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A313" s="4">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A313">
         <v>30</v>
       </c>
       <c r="B313">
@@ -6234,12 +8434,12 @@
       <c r="D313">
         <v>14</v>
       </c>
-      <c r="E313" s="2">
+      <c r="E313">
         <v>39.930695833333338</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A314" s="4">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A314">
         <v>30</v>
       </c>
       <c r="B314">
@@ -6251,12 +8451,12 @@
       <c r="D314">
         <v>15</v>
       </c>
-      <c r="E314" s="2">
+      <c r="E314">
         <v>43.071042500000004</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A315" s="4">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A315">
         <v>30</v>
       </c>
       <c r="B315">
@@ -6268,12 +8468,12 @@
       <c r="D315">
         <v>16</v>
       </c>
-      <c r="E315" s="2">
+      <c r="E315">
         <v>41.284220833333336</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A316" s="4">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A316">
         <v>30</v>
       </c>
       <c r="B316">
@@ -6285,12 +8485,12 @@
       <c r="D316">
         <v>17</v>
       </c>
-      <c r="E316" s="2">
+      <c r="E316">
         <v>40.396162499999996</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A317" s="4">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A317">
         <v>30</v>
       </c>
       <c r="B317">
@@ -6302,12 +8502,12 @@
       <c r="D317">
         <v>18</v>
       </c>
-      <c r="E317" s="2">
+      <c r="E317">
         <v>39.649014583333326</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A318" s="4">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A318">
         <v>30</v>
       </c>
       <c r="B318">
@@ -6319,12 +8519,12 @@
       <c r="D318">
         <v>19</v>
       </c>
-      <c r="E318" s="2">
+      <c r="E318">
         <v>38.624235416666671</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A319" s="4">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A319">
         <v>30</v>
       </c>
       <c r="B319">
@@ -6336,12 +8536,12 @@
       <c r="D319">
         <v>20</v>
       </c>
-      <c r="E319" s="2">
+      <c r="E319">
         <v>40.130850000000002</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A320" s="4">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A320">
         <v>30</v>
       </c>
       <c r="B320">
@@ -6353,12 +8553,12 @@
       <c r="D320">
         <v>21</v>
       </c>
-      <c r="E320" s="2">
+      <c r="E320">
         <v>40.892031249999995</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A321" s="4">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A321">
         <v>30</v>
       </c>
       <c r="B321">
@@ -6370,12 +8570,12 @@
       <c r="D321">
         <v>22</v>
       </c>
-      <c r="E321" s="2">
+      <c r="E321">
         <v>39.834895833333327</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A322" s="4">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A322">
         <v>30</v>
       </c>
       <c r="B322">
@@ -6387,12 +8587,12 @@
       <c r="D322">
         <v>23</v>
       </c>
-      <c r="E322" s="2">
+      <c r="E322">
         <v>39.614008333333338</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A323" s="4">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A323">
         <v>30</v>
       </c>
       <c r="B323">
@@ -6404,12 +8604,12 @@
       <c r="D323">
         <v>24</v>
       </c>
-      <c r="E323" s="2">
+      <c r="E323">
         <v>38.565970833333331</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A324" s="4">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A324">
         <v>30</v>
       </c>
       <c r="B324">
@@ -6421,12 +8621,12 @@
       <c r="D324">
         <v>25</v>
       </c>
-      <c r="E324" s="2">
+      <c r="E324">
         <v>37.45817916666666</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A325" s="4">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A325">
         <v>30</v>
       </c>
       <c r="B325">
@@ -6438,12 +8638,12 @@
       <c r="D325">
         <v>26</v>
       </c>
-      <c r="E325" s="2">
+      <c r="E325">
         <v>38.100518750000006</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A326" s="4">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A326">
         <v>30</v>
       </c>
       <c r="B326">
@@ -6455,12 +8655,12 @@
       <c r="D326">
         <v>27</v>
       </c>
-      <c r="E326" s="2">
+      <c r="E326">
         <v>38.857658333333326</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A327" s="4">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A327">
         <v>30</v>
       </c>
       <c r="B327">
@@ -6472,12 +8672,12 @@
       <c r="D327">
         <v>28</v>
       </c>
-      <c r="E327" s="2">
+      <c r="E327">
         <v>40.107954166666666</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A328" s="4">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A328">
         <v>30</v>
       </c>
       <c r="B328">
@@ -6489,12 +8689,12 @@
       <c r="D328">
         <v>29</v>
       </c>
-      <c r="E328" s="2">
+      <c r="E328">
         <v>40.295762500000002</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A329" s="4">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A329">
         <v>30</v>
       </c>
       <c r="B329">
@@ -6506,12 +8706,12 @@
       <c r="D329">
         <v>30</v>
       </c>
-      <c r="E329" s="2">
+      <c r="E329">
         <v>38.987212500000005</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A330" s="4">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A330">
         <v>30</v>
       </c>
       <c r="B330">
@@ -6523,12 +8723,12 @@
       <c r="D330">
         <v>1</v>
       </c>
-      <c r="E330" s="3">
+      <c r="E330">
         <v>38.121416666666654</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A331" s="4">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A331">
         <v>30</v>
       </c>
       <c r="B331">
@@ -6540,12 +8740,12 @@
       <c r="D331">
         <v>2</v>
       </c>
-      <c r="E331" s="3">
+      <c r="E331">
         <v>40.494114583333342</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A332" s="4">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A332">
         <v>30</v>
       </c>
       <c r="B332">
@@ -6557,12 +8757,12 @@
       <c r="D332">
         <v>3</v>
       </c>
-      <c r="E332" s="3">
+      <c r="E332">
         <v>41.521456250000007</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A333" s="4">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A333">
         <v>30</v>
       </c>
       <c r="B333">
@@ -6574,12 +8774,12 @@
       <c r="D333">
         <v>4</v>
       </c>
-      <c r="E333" s="3">
+      <c r="E333">
         <v>41.320939583333335</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A334" s="4">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A334">
         <v>30</v>
       </c>
       <c r="B334">
@@ -6591,12 +8791,12 @@
       <c r="D334">
         <v>5</v>
       </c>
-      <c r="E334" s="3">
+      <c r="E334">
         <v>40.903390909090916</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A335" s="4">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A335">
         <v>30</v>
       </c>
       <c r="B335">
@@ -6608,12 +8808,12 @@
       <c r="D335">
         <v>6</v>
       </c>
-      <c r="E335" s="3">
+      <c r="E335">
         <v>41.556806249999994</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A336" s="4">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A336">
         <v>30</v>
       </c>
       <c r="B336">
@@ -6625,12 +8825,12 @@
       <c r="D336">
         <v>7</v>
       </c>
-      <c r="E336" s="3">
+      <c r="E336">
         <v>41.487068749999985</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A337" s="4">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A337">
         <v>30</v>
       </c>
       <c r="B337">
@@ -6642,12 +8842,12 @@
       <c r="D337">
         <v>8</v>
       </c>
-      <c r="E337" s="3">
+      <c r="E337">
         <v>40.106562499999995</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A338" s="4">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A338">
         <v>30</v>
       </c>
       <c r="B338">
@@ -6659,12 +8859,12 @@
       <c r="D338">
         <v>9</v>
       </c>
-      <c r="E338" s="3">
+      <c r="E338">
         <v>40.912622916666663</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A339" s="4">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A339">
         <v>30</v>
       </c>
       <c r="B339">
@@ -6676,12 +8876,12 @@
       <c r="D339">
         <v>10</v>
       </c>
-      <c r="E339" s="3">
+      <c r="E339">
         <v>41.050587499999999</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A340" s="4">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A340">
         <v>30</v>
       </c>
       <c r="B340">
@@ -6693,12 +8893,12 @@
       <c r="D340">
         <v>11</v>
       </c>
-      <c r="E340" s="3">
+      <c r="E340">
         <v>41.461433333333332</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A341" s="4">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A341">
         <v>30</v>
       </c>
       <c r="B341">
@@ -6710,12 +8910,12 @@
       <c r="D341">
         <v>12</v>
       </c>
-      <c r="E341" s="3">
+      <c r="E341">
         <v>41.316927083333333</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A342" s="4">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A342">
         <v>30</v>
       </c>
       <c r="B342">
@@ -6727,12 +8927,12 @@
       <c r="D342">
         <v>13</v>
       </c>
-      <c r="E342" s="3">
+      <c r="E342">
         <v>42.214706249999999</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A343" s="4">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A343">
         <v>30</v>
       </c>
       <c r="B343">
@@ -6744,12 +8944,12 @@
       <c r="D343">
         <v>14</v>
       </c>
-      <c r="E343" s="3">
+      <c r="E343">
         <v>41.724706250000004</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A344" s="4">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A344">
         <v>30</v>
       </c>
       <c r="B344">
@@ -6761,12 +8961,12 @@
       <c r="D344">
         <v>15</v>
       </c>
-      <c r="E344" s="3">
+      <c r="E344">
         <v>40.550508333333326</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A345" s="4">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A345">
         <v>30</v>
       </c>
       <c r="B345">
@@ -6778,12 +8978,12 @@
       <c r="D345">
         <v>16</v>
       </c>
-      <c r="E345" s="3">
+      <c r="E345">
         <v>39.657872499999996</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A346" s="4">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A346">
         <v>30</v>
       </c>
       <c r="B346">
@@ -6795,12 +8995,12 @@
       <c r="D346">
         <v>17</v>
       </c>
-      <c r="E346" s="3">
+      <c r="E346">
         <v>39.038333333333334</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A347" s="4">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A347">
         <v>30</v>
       </c>
       <c r="B347">
@@ -6812,12 +9012,12 @@
       <c r="D347">
         <v>18</v>
       </c>
-      <c r="E347" s="3">
+      <c r="E347">
         <v>39.737516666666664</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A348" s="4">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A348">
         <v>30</v>
       </c>
       <c r="B348">
@@ -6829,12 +9029,12 @@
       <c r="D348">
         <v>19</v>
       </c>
-      <c r="E348" s="3">
+      <c r="E348">
         <v>39.826684210526317</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A349" s="4">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A349">
         <v>30</v>
       </c>
       <c r="B349">
@@ -6846,12 +9046,12 @@
       <c r="D349">
         <v>20</v>
       </c>
-      <c r="E349" s="3">
+      <c r="E349">
         <v>41.034704166666664</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A350" s="4">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A350">
         <v>30</v>
       </c>
       <c r="B350">
@@ -6863,12 +9063,12 @@
       <c r="D350">
         <v>21</v>
       </c>
-      <c r="E350" s="3">
+      <c r="E350">
         <v>41.426093750000007</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A351" s="4">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A351">
         <v>30</v>
       </c>
       <c r="B351">
@@ -6880,12 +9080,12 @@
       <c r="D351">
         <v>22</v>
       </c>
-      <c r="E351" s="3">
+      <c r="E351">
         <v>40.133804166666678</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A352" s="4">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A352">
         <v>30</v>
       </c>
       <c r="B352">
@@ -6897,12 +9097,12 @@
       <c r="D352">
         <v>23</v>
       </c>
-      <c r="E352" s="3">
+      <c r="E352">
         <v>40.283127083333333</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A353" s="4">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A353">
         <v>30</v>
       </c>
       <c r="B353">
@@ -6914,12 +9114,12 @@
       <c r="D353">
         <v>24</v>
       </c>
-      <c r="E353" s="3">
+      <c r="E353">
         <v>40.736441666666671</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A354" s="4">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A354">
         <v>30</v>
       </c>
       <c r="B354">
@@ -6931,12 +9131,12 @@
       <c r="D354">
         <v>25</v>
       </c>
-      <c r="E354" s="3">
+      <c r="E354">
         <v>39.704927083333331</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A355" s="4">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A355">
         <v>30</v>
       </c>
       <c r="B355">
@@ -6948,12 +9148,12 @@
       <c r="D355">
         <v>26</v>
       </c>
-      <c r="E355" s="3">
+      <c r="E355">
         <v>38.572920833333335</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A356" s="4">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A356">
         <v>30</v>
       </c>
       <c r="B356">
@@ -6965,12 +9165,12 @@
       <c r="D356">
         <v>27</v>
       </c>
-      <c r="E356" s="3">
+      <c r="E356">
         <v>36.853506250000002</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A357" s="4">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A357">
         <v>30</v>
       </c>
       <c r="B357">
@@ -6982,12 +9182,12 @@
       <c r="D357">
         <v>28</v>
       </c>
-      <c r="E357" s="3">
+      <c r="E357">
         <v>34.042012499999991</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A358" s="4">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A358">
         <v>30</v>
       </c>
       <c r="B358">
@@ -6999,12 +9199,12 @@
       <c r="D358">
         <v>29</v>
       </c>
-      <c r="E358" s="3">
+      <c r="E358">
         <v>31.083460416666668</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A359" s="4">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A359">
         <v>30</v>
       </c>
       <c r="B359">
@@ -7016,12 +9216,12 @@
       <c r="D359">
         <v>30</v>
       </c>
-      <c r="E359" s="3">
+      <c r="E359">
         <v>28.825729166666665</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A360" s="4">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A360">
         <v>30</v>
       </c>
       <c r="B360">
@@ -7033,12 +9233,12 @@
       <c r="D360">
         <v>31</v>
       </c>
-      <c r="E360" s="3">
+      <c r="E360">
         <v>27.386275000000001</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A361" s="4">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A361">
         <v>30</v>
       </c>
       <c r="B361">
@@ -7050,12 +9250,12 @@
       <c r="D361">
         <v>1</v>
       </c>
-      <c r="E361" s="5">
+      <c r="E361">
         <v>26.241041666666661</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A362" s="4">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A362">
         <v>30</v>
       </c>
       <c r="B362">
@@ -7067,12 +9267,12 @@
       <c r="D362">
         <v>2</v>
       </c>
-      <c r="E362" s="5">
+      <c r="E362">
         <v>25.3863375</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A363" s="4">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A363">
         <v>30</v>
       </c>
       <c r="B363">
@@ -7084,12 +9284,12 @@
       <c r="D363">
         <v>3</v>
       </c>
-      <c r="E363" s="5">
+      <c r="E363">
         <v>24.923489583333335</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A364" s="4">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A364">
         <v>30</v>
       </c>
       <c r="B364">
@@ -7101,12 +9301,12 @@
       <c r="D364">
         <v>4</v>
       </c>
-      <c r="E364" s="5">
+      <c r="E364">
         <v>24.503662500000001</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A365" s="4">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A365">
         <v>30</v>
       </c>
       <c r="B365">
@@ -7118,1498 +9318,1499 @@
       <c r="D365">
         <v>5</v>
       </c>
-      <c r="E365" s="5">
+      <c r="E365">
         <v>24.220284090909093</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A366">
         <v>29</v>
       </c>
-      <c r="B366" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C366" s="4">
-        <v>5</v>
-      </c>
-      <c r="D366" s="4">
+      <c r="B366">
+        <v>2018</v>
+      </c>
+      <c r="C366">
+        <v>5</v>
+      </c>
+      <c r="D366">
         <v>11</v>
       </c>
-      <c r="E366" s="6">
+      <c r="E366">
         <v>41.510972222222222</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A367" s="4">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A367">
         <v>29</v>
       </c>
-      <c r="B367" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C367" s="4">
-        <v>5</v>
-      </c>
-      <c r="D367" s="4">
+      <c r="B367">
+        <v>2018</v>
+      </c>
+      <c r="C367">
+        <v>5</v>
+      </c>
+      <c r="D367">
         <v>12</v>
       </c>
-      <c r="E367" s="6">
+      <c r="E367">
         <v>41.959254166666661</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A368" s="4">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A368">
         <v>29</v>
       </c>
-      <c r="B368" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C368" s="4">
-        <v>5</v>
-      </c>
-      <c r="D368" s="4">
+      <c r="B368">
+        <v>2018</v>
+      </c>
+      <c r="C368">
+        <v>5</v>
+      </c>
+      <c r="D368">
         <v>13</v>
       </c>
-      <c r="E368" s="6">
+      <c r="E368">
         <v>42.261266666666664</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A369" s="4">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A369">
         <v>29</v>
       </c>
-      <c r="B369" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C369" s="4">
-        <v>5</v>
-      </c>
-      <c r="D369" s="4">
+      <c r="B369">
+        <v>2018</v>
+      </c>
+      <c r="C369">
+        <v>5</v>
+      </c>
+      <c r="D369">
         <v>14</v>
       </c>
-      <c r="E369" s="6">
+      <c r="E369">
         <v>42.507412500000001</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A370" s="4">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A370">
         <v>29</v>
       </c>
-      <c r="B370" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C370" s="4">
-        <v>5</v>
-      </c>
-      <c r="D370" s="4">
+      <c r="B370">
+        <v>2018</v>
+      </c>
+      <c r="C370">
+        <v>5</v>
+      </c>
+      <c r="D370">
         <v>15</v>
       </c>
-      <c r="E370" s="6">
+      <c r="E370">
         <v>42.257554166666665</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A371" s="4">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A371">
         <v>29</v>
       </c>
-      <c r="B371" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C371" s="4">
-        <v>5</v>
-      </c>
-      <c r="D371" s="4">
+      <c r="B371">
+        <v>2018</v>
+      </c>
+      <c r="C371">
+        <v>5</v>
+      </c>
+      <c r="D371">
         <v>16</v>
       </c>
-      <c r="E371" s="6">
+      <c r="E371">
         <v>41.507310416666662</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A372" s="4">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A372">
         <v>29</v>
       </c>
-      <c r="B372" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C372" s="4">
-        <v>5</v>
-      </c>
-      <c r="D372" s="4">
+      <c r="B372">
+        <v>2018</v>
+      </c>
+      <c r="C372">
+        <v>5</v>
+      </c>
+      <c r="D372">
         <v>17</v>
       </c>
-      <c r="E372" s="6">
+      <c r="E372">
         <v>41.504774999999988</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A373" s="4">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A373">
         <v>29</v>
       </c>
-      <c r="B373" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C373" s="4">
-        <v>5</v>
-      </c>
-      <c r="D373" s="4">
+      <c r="B373">
+        <v>2018</v>
+      </c>
+      <c r="C373">
+        <v>5</v>
+      </c>
+      <c r="D373">
         <v>18</v>
       </c>
-      <c r="E373" s="6">
+      <c r="E373">
         <v>41.831006249999994</v>
       </c>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A374" s="4">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A374">
         <v>29</v>
       </c>
-      <c r="B374" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C374" s="4">
-        <v>5</v>
-      </c>
-      <c r="D374" s="4">
+      <c r="B374">
+        <v>2018</v>
+      </c>
+      <c r="C374">
+        <v>5</v>
+      </c>
+      <c r="D374">
         <v>19</v>
       </c>
-      <c r="E374" s="6">
+      <c r="E374">
         <v>42.062902083333334</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A375" s="4">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A375">
         <v>29</v>
       </c>
-      <c r="B375" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C375" s="4">
-        <v>5</v>
-      </c>
-      <c r="D375" s="4">
+      <c r="B375">
+        <v>2018</v>
+      </c>
+      <c r="C375">
+        <v>5</v>
+      </c>
+      <c r="D375">
         <v>20</v>
       </c>
-      <c r="E375" s="6">
+      <c r="E375">
         <v>42.12088541666666</v>
       </c>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A376" s="4">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A376">
         <v>29</v>
       </c>
-      <c r="B376" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C376" s="4">
-        <v>5</v>
-      </c>
-      <c r="D376" s="4">
+      <c r="B376">
+        <v>2018</v>
+      </c>
+      <c r="C376">
+        <v>5</v>
+      </c>
+      <c r="D376">
         <v>21</v>
       </c>
-      <c r="E376" s="6">
+      <c r="E376">
         <v>42.116454166666678</v>
       </c>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A377" s="4">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A377">
         <v>29</v>
       </c>
-      <c r="B377" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C377" s="4">
-        <v>5</v>
-      </c>
-      <c r="D377" s="4">
+      <c r="B377">
+        <v>2018</v>
+      </c>
+      <c r="C377">
+        <v>5</v>
+      </c>
+      <c r="D377">
         <v>22</v>
       </c>
-      <c r="E377" s="6">
+      <c r="E377">
         <v>41.68831458333333</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A378" s="4">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A378">
         <v>29</v>
       </c>
-      <c r="B378" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C378" s="4">
-        <v>5</v>
-      </c>
-      <c r="D378" s="4">
+      <c r="B378">
+        <v>2018</v>
+      </c>
+      <c r="C378">
+        <v>5</v>
+      </c>
+      <c r="D378">
         <v>23</v>
       </c>
-      <c r="E378" s="6">
+      <c r="E378">
         <v>41.494635714285714</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A379" s="4">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A379">
         <v>29</v>
       </c>
-      <c r="B379" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C379" s="4">
-        <v>5</v>
-      </c>
-      <c r="D379" s="4">
+      <c r="B379">
+        <v>2018</v>
+      </c>
+      <c r="C379">
+        <v>5</v>
+      </c>
+      <c r="D379">
         <v>24</v>
       </c>
-      <c r="E379" s="6">
+      <c r="E379">
         <v>42.487021428571431</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A380" s="4">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A380">
         <v>29</v>
       </c>
-      <c r="B380" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C380" s="4">
-        <v>5</v>
-      </c>
-      <c r="D380" s="4">
+      <c r="B380">
+        <v>2018</v>
+      </c>
+      <c r="C380">
+        <v>5</v>
+      </c>
+      <c r="D380">
         <v>25</v>
       </c>
-      <c r="E380" s="6">
+      <c r="E380">
         <v>42.729029166666663</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A381" s="4">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A381">
         <v>29</v>
       </c>
-      <c r="B381" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C381" s="4">
-        <v>5</v>
-      </c>
-      <c r="D381" s="4">
+      <c r="B381">
+        <v>2018</v>
+      </c>
+      <c r="C381">
+        <v>5</v>
+      </c>
+      <c r="D381">
         <v>26</v>
       </c>
-      <c r="E381" s="6">
+      <c r="E381">
         <v>42.974843750000012</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A382" s="4">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A382">
         <v>29</v>
       </c>
-      <c r="B382" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C382" s="4">
-        <v>5</v>
-      </c>
-      <c r="D382" s="4">
-        <v>27</v>
-      </c>
-      <c r="E382" s="6">
+      <c r="B382">
+        <v>2018</v>
+      </c>
+      <c r="C382">
+        <v>5</v>
+      </c>
+      <c r="D382">
+        <v>27</v>
+      </c>
+      <c r="E382">
         <v>43.361562499999991</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A383" s="4">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A383">
         <v>29</v>
       </c>
-      <c r="B383" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C383" s="4">
-        <v>5</v>
-      </c>
-      <c r="D383" s="4">
-        <v>28</v>
-      </c>
-      <c r="E383" s="6">
+      <c r="B383">
+        <v>2018</v>
+      </c>
+      <c r="C383">
+        <v>5</v>
+      </c>
+      <c r="D383">
+        <v>28</v>
+      </c>
+      <c r="E383">
         <v>43.530752380952379</v>
       </c>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A384" s="4">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A384">
         <v>29</v>
       </c>
-      <c r="B384" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C384" s="4">
-        <v>5</v>
-      </c>
-      <c r="D384" s="4">
+      <c r="B384">
+        <v>2018</v>
+      </c>
+      <c r="C384">
+        <v>5</v>
+      </c>
+      <c r="D384">
         <v>29</v>
       </c>
-      <c r="E384" s="6">
+      <c r="E384">
         <v>43.693214285714284</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A385" s="4">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A385">
         <v>29</v>
       </c>
-      <c r="B385" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C385" s="4">
-        <v>5</v>
-      </c>
-      <c r="D385" s="4">
+      <c r="B385">
+        <v>2018</v>
+      </c>
+      <c r="C385">
+        <v>5</v>
+      </c>
+      <c r="D385">
         <v>30</v>
       </c>
-      <c r="E385" s="6">
+      <c r="E385">
         <v>43.472710714285711</v>
       </c>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A386" s="4">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A386">
         <v>29</v>
       </c>
-      <c r="B386" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C386" s="4">
-        <v>5</v>
-      </c>
-      <c r="D386" s="4">
+      <c r="B386">
+        <v>2018</v>
+      </c>
+      <c r="C386">
+        <v>5</v>
+      </c>
+      <c r="D386">
         <v>31</v>
       </c>
-      <c r="E386" s="6">
+      <c r="E386">
         <v>43.174980000000005</v>
       </c>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A387" s="4">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A387">
         <v>29</v>
       </c>
-      <c r="B387" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C387" s="4">
-        <v>6</v>
-      </c>
-      <c r="D387" s="4">
+      <c r="B387">
+        <v>2018</v>
+      </c>
+      <c r="C387">
+        <v>6</v>
+      </c>
+      <c r="D387">
         <v>1</v>
       </c>
-      <c r="E387" s="7">
+      <c r="E387">
         <v>42.811390476190475</v>
       </c>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A388" s="4">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A388">
         <v>29</v>
       </c>
-      <c r="B388" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C388" s="4">
-        <v>6</v>
-      </c>
-      <c r="D388" s="4">
+      <c r="B388">
+        <v>2018</v>
+      </c>
+      <c r="C388">
+        <v>6</v>
+      </c>
+      <c r="D388">
         <v>2</v>
       </c>
-      <c r="E388" s="7">
+      <c r="E388">
         <v>42.446414999999995</v>
       </c>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A389" s="4">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A389">
         <v>29</v>
       </c>
-      <c r="B389" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C389" s="4">
-        <v>6</v>
-      </c>
-      <c r="D389" s="4">
+      <c r="B389">
+        <v>2018</v>
+      </c>
+      <c r="C389">
+        <v>6</v>
+      </c>
+      <c r="D389">
         <v>3</v>
       </c>
-      <c r="E389" s="7">
+      <c r="E389">
         <v>41.877272500000004</v>
       </c>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A390" s="4">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A390">
         <v>29</v>
       </c>
-      <c r="B390" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C390" s="4">
-        <v>6</v>
-      </c>
-      <c r="D390" s="4">
+      <c r="B390">
+        <v>2018</v>
+      </c>
+      <c r="C390">
+        <v>6</v>
+      </c>
+      <c r="D390">
         <v>4</v>
       </c>
-      <c r="E390" s="7">
+      <c r="E390">
         <v>41.083562500000006</v>
       </c>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A391" s="4">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A391">
         <v>29</v>
       </c>
-      <c r="B391" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C391" s="4">
-        <v>6</v>
-      </c>
-      <c r="D391" s="4">
-        <v>5</v>
-      </c>
-      <c r="E391" s="7">
+      <c r="B391">
+        <v>2018</v>
+      </c>
+      <c r="C391">
+        <v>6</v>
+      </c>
+      <c r="D391">
+        <v>5</v>
+      </c>
+      <c r="E391">
         <v>39.908275000000003</v>
       </c>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A392" s="4">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A392">
         <v>29</v>
       </c>
-      <c r="B392" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C392" s="4">
-        <v>6</v>
-      </c>
-      <c r="D392" s="4">
-        <v>6</v>
-      </c>
-      <c r="E392" s="7">
+      <c r="B392">
+        <v>2018</v>
+      </c>
+      <c r="C392">
+        <v>6</v>
+      </c>
+      <c r="D392">
+        <v>6</v>
+      </c>
+      <c r="E392">
         <v>38.772549999999995</v>
       </c>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A393" s="4">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A393">
         <v>29</v>
       </c>
-      <c r="B393" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C393" s="4">
-        <v>6</v>
-      </c>
-      <c r="D393" s="4">
-        <v>7</v>
-      </c>
-      <c r="E393" s="7">
+      <c r="B393">
+        <v>2018</v>
+      </c>
+      <c r="C393">
+        <v>6</v>
+      </c>
+      <c r="D393">
+        <v>7</v>
+      </c>
+      <c r="E393">
         <v>37.392376470588232</v>
       </c>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A394" s="4">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A394">
         <v>29</v>
       </c>
-      <c r="B394" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C394" s="4">
-        <v>6</v>
-      </c>
-      <c r="D394" s="4">
+      <c r="B394">
+        <v>2018</v>
+      </c>
+      <c r="C394">
+        <v>6</v>
+      </c>
+      <c r="D394">
         <v>8</v>
       </c>
-      <c r="E394" s="7">
+      <c r="E394">
         <v>37.843442105263158</v>
       </c>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A395" s="4">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A395">
         <v>29</v>
       </c>
-      <c r="B395" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C395" s="4">
-        <v>6</v>
-      </c>
-      <c r="D395" s="4">
+      <c r="B395">
+        <v>2018</v>
+      </c>
+      <c r="C395">
+        <v>6</v>
+      </c>
+      <c r="D395">
         <v>9</v>
       </c>
-      <c r="E395" s="7">
+      <c r="E395">
         <v>43.32203684210527</v>
       </c>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A396" s="4">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A396">
         <v>29</v>
       </c>
-      <c r="B396" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C396" s="4">
-        <v>6</v>
-      </c>
-      <c r="D396" s="4">
+      <c r="B396">
+        <v>2018</v>
+      </c>
+      <c r="C396">
+        <v>6</v>
+      </c>
+      <c r="D396">
         <v>10</v>
       </c>
-      <c r="E396" s="7">
+      <c r="E396">
         <v>42.589812500000008</v>
       </c>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A397" s="4">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A397">
         <v>29</v>
       </c>
-      <c r="B397" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C397" s="4">
-        <v>6</v>
-      </c>
-      <c r="D397" s="4">
+      <c r="B397">
+        <v>2018</v>
+      </c>
+      <c r="C397">
+        <v>6</v>
+      </c>
+      <c r="D397">
         <v>11</v>
       </c>
-      <c r="E397" s="7">
+      <c r="E397">
         <v>41.960541176470585</v>
       </c>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A398" s="4">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A398">
         <v>29</v>
       </c>
-      <c r="B398" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C398" s="4">
-        <v>6</v>
-      </c>
-      <c r="D398" s="4">
+      <c r="B398">
+        <v>2018</v>
+      </c>
+      <c r="C398">
+        <v>6</v>
+      </c>
+      <c r="D398">
         <v>12</v>
       </c>
-      <c r="E398" s="7">
+      <c r="E398">
         <v>41.050815909090907</v>
       </c>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A399" s="4">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A399">
         <v>29</v>
       </c>
-      <c r="B399" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C399" s="4">
-        <v>6</v>
-      </c>
-      <c r="D399" s="4">
+      <c r="B399">
+        <v>2018</v>
+      </c>
+      <c r="C399">
+        <v>6</v>
+      </c>
+      <c r="D399">
         <v>13</v>
       </c>
-      <c r="E399" s="7">
+      <c r="E399">
         <v>39.999235416666671</v>
       </c>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A400" s="4">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A400">
         <v>29</v>
       </c>
-      <c r="B400" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C400" s="4">
-        <v>6</v>
-      </c>
-      <c r="D400" s="4">
+      <c r="B400">
+        <v>2018</v>
+      </c>
+      <c r="C400">
+        <v>6</v>
+      </c>
+      <c r="D400">
         <v>14</v>
       </c>
-      <c r="E400" s="7">
+      <c r="E400">
         <v>39.066231250000008</v>
       </c>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A401" s="4">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A401">
         <v>29</v>
       </c>
-      <c r="B401" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C401" s="4">
-        <v>6</v>
-      </c>
-      <c r="D401" s="4">
+      <c r="B401">
+        <v>2018</v>
+      </c>
+      <c r="C401">
+        <v>6</v>
+      </c>
+      <c r="D401">
         <v>15</v>
       </c>
-      <c r="E401" s="7">
+      <c r="E401">
         <v>41.981517499999988</v>
       </c>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A402" s="4">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A402">
         <v>29</v>
       </c>
-      <c r="B402" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C402" s="4">
-        <v>6</v>
-      </c>
-      <c r="D402" s="4">
+      <c r="B402">
+        <v>2018</v>
+      </c>
+      <c r="C402">
+        <v>6</v>
+      </c>
+      <c r="D402">
         <v>16</v>
       </c>
-      <c r="E402" s="7">
+      <c r="E402">
         <v>41.82480833333333</v>
       </c>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A403" s="4">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A403">
         <v>29</v>
       </c>
-      <c r="B403" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C403" s="4">
-        <v>6</v>
-      </c>
-      <c r="D403" s="4">
+      <c r="B403">
+        <v>2018</v>
+      </c>
+      <c r="C403">
+        <v>6</v>
+      </c>
+      <c r="D403">
         <v>17</v>
       </c>
-      <c r="E403" s="7">
+      <c r="E403">
         <v>41.156995833333333</v>
       </c>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A404" s="4">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A404">
         <v>29</v>
       </c>
-      <c r="B404" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C404" s="4">
-        <v>6</v>
-      </c>
-      <c r="D404" s="4">
+      <c r="B404">
+        <v>2018</v>
+      </c>
+      <c r="C404">
+        <v>6</v>
+      </c>
+      <c r="D404">
         <v>18</v>
       </c>
-      <c r="E404" s="7">
+      <c r="E404">
         <v>40.488139583333336</v>
       </c>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A405" s="4">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A405">
         <v>29</v>
       </c>
-      <c r="B405" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C405" s="4">
-        <v>6</v>
-      </c>
-      <c r="D405" s="4">
+      <c r="B405">
+        <v>2018</v>
+      </c>
+      <c r="C405">
+        <v>6</v>
+      </c>
+      <c r="D405">
         <v>19</v>
       </c>
-      <c r="E405" s="7">
+      <c r="E405">
         <v>39.788574999999994</v>
       </c>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A406" s="4">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A406">
         <v>29</v>
       </c>
-      <c r="B406" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C406" s="4">
-        <v>6</v>
-      </c>
-      <c r="D406" s="4">
+      <c r="B406">
+        <v>2018</v>
+      </c>
+      <c r="C406">
+        <v>6</v>
+      </c>
+      <c r="D406">
         <v>20</v>
       </c>
-      <c r="E406" s="7">
+      <c r="E406">
         <v>39.633997916666658</v>
       </c>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A407" s="4">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A407">
         <v>29</v>
       </c>
-      <c r="B407" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C407" s="4">
-        <v>6</v>
-      </c>
-      <c r="D407" s="4">
+      <c r="B407">
+        <v>2018</v>
+      </c>
+      <c r="C407">
+        <v>6</v>
+      </c>
+      <c r="D407">
         <v>21</v>
       </c>
-      <c r="E407" s="7">
+      <c r="E407">
         <v>39.808925000000002</v>
       </c>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A408" s="4">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A408">
         <v>29</v>
       </c>
-      <c r="B408" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C408" s="4">
-        <v>6</v>
-      </c>
-      <c r="D408" s="4">
+      <c r="B408">
+        <v>2018</v>
+      </c>
+      <c r="C408">
+        <v>6</v>
+      </c>
+      <c r="D408">
         <v>22</v>
       </c>
-      <c r="E408" s="7">
+      <c r="E408">
         <v>39.024985416666667</v>
       </c>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A409" s="4">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A409">
         <v>29</v>
       </c>
-      <c r="B409" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C409" s="4">
-        <v>6</v>
-      </c>
-      <c r="D409" s="4">
+      <c r="B409">
+        <v>2018</v>
+      </c>
+      <c r="C409">
+        <v>6</v>
+      </c>
+      <c r="D409">
         <v>23</v>
       </c>
-      <c r="E409" s="7">
+      <c r="E409">
         <v>38.122287499999992</v>
       </c>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A410" s="4">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A410">
         <v>29</v>
       </c>
-      <c r="B410" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C410" s="4">
-        <v>6</v>
-      </c>
-      <c r="D410" s="4">
+      <c r="B410">
+        <v>2018</v>
+      </c>
+      <c r="C410">
+        <v>6</v>
+      </c>
+      <c r="D410">
         <v>24</v>
       </c>
-      <c r="E410" s="7">
+      <c r="E410">
         <v>37.540831249999989</v>
       </c>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A411" s="4">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A411">
         <v>29</v>
       </c>
-      <c r="B411" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C411" s="4">
-        <v>6</v>
-      </c>
-      <c r="D411" s="4">
+      <c r="B411">
+        <v>2018</v>
+      </c>
+      <c r="C411">
+        <v>6</v>
+      </c>
+      <c r="D411">
         <v>25</v>
       </c>
-      <c r="E411" s="7">
+      <c r="E411">
         <v>36.611650000000004</v>
       </c>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A412" s="4">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A412">
         <v>29</v>
       </c>
-      <c r="B412" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C412" s="4">
-        <v>6</v>
-      </c>
-      <c r="D412" s="4">
+      <c r="B412">
+        <v>2018</v>
+      </c>
+      <c r="C412">
+        <v>6</v>
+      </c>
+      <c r="D412">
         <v>26</v>
       </c>
-      <c r="E412" s="7">
+      <c r="E412">
         <v>35.42160208333334</v>
       </c>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A413" s="4">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A413">
         <v>29</v>
       </c>
-      <c r="B413" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C413" s="4">
-        <v>6</v>
-      </c>
-      <c r="D413" s="4">
-        <v>27</v>
-      </c>
-      <c r="E413" s="7">
+      <c r="B413">
+        <v>2018</v>
+      </c>
+      <c r="C413">
+        <v>6</v>
+      </c>
+      <c r="D413">
+        <v>27</v>
+      </c>
+      <c r="E413">
         <v>34.16530208333333</v>
       </c>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A414" s="4">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A414">
         <v>29</v>
       </c>
-      <c r="B414" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C414" s="4">
-        <v>6</v>
-      </c>
-      <c r="D414" s="4">
-        <v>28</v>
-      </c>
-      <c r="E414" s="7">
+      <c r="B414">
+        <v>2018</v>
+      </c>
+      <c r="C414">
+        <v>6</v>
+      </c>
+      <c r="D414">
+        <v>28</v>
+      </c>
+      <c r="E414">
         <v>32.812879166666669</v>
       </c>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A415" s="4">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A415">
         <v>29</v>
       </c>
-      <c r="B415" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C415" s="4">
-        <v>6</v>
-      </c>
-      <c r="D415" s="4">
+      <c r="B415">
+        <v>2018</v>
+      </c>
+      <c r="C415">
+        <v>6</v>
+      </c>
+      <c r="D415">
         <v>29</v>
       </c>
-      <c r="E415" s="7">
+      <c r="E415">
         <v>31.876722916666665</v>
       </c>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A416" s="4">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A416">
         <v>29</v>
       </c>
-      <c r="B416" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C416" s="4">
-        <v>6</v>
-      </c>
-      <c r="D416" s="4">
+      <c r="B416">
+        <v>2018</v>
+      </c>
+      <c r="C416">
+        <v>6</v>
+      </c>
+      <c r="D416">
         <v>30</v>
       </c>
-      <c r="E416" s="7">
+      <c r="E416">
         <v>31.026891666666671</v>
       </c>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A417" s="4">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A417">
         <v>29</v>
       </c>
-      <c r="B417" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C417" s="4">
-        <v>7</v>
-      </c>
-      <c r="D417" s="4">
+      <c r="B417">
+        <v>2018</v>
+      </c>
+      <c r="C417">
+        <v>7</v>
+      </c>
+      <c r="D417">
         <v>1</v>
       </c>
-      <c r="E417" s="8">
+      <c r="E417">
         <v>30.523733333333329</v>
       </c>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A418" s="4">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A418">
         <v>29</v>
       </c>
-      <c r="B418" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C418" s="4">
-        <v>7</v>
-      </c>
-      <c r="D418" s="4">
+      <c r="B418">
+        <v>2018</v>
+      </c>
+      <c r="C418">
+        <v>7</v>
+      </c>
+      <c r="D418">
         <v>2</v>
       </c>
-      <c r="E418" s="8">
+      <c r="E418">
         <v>29.938385416666662</v>
       </c>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A419" s="4">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A419">
         <v>29</v>
       </c>
-      <c r="B419" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C419" s="4">
-        <v>7</v>
-      </c>
-      <c r="D419" s="4">
+      <c r="B419">
+        <v>2018</v>
+      </c>
+      <c r="C419">
+        <v>7</v>
+      </c>
+      <c r="D419">
         <v>3</v>
       </c>
-      <c r="E419" s="8">
+      <c r="E419">
         <v>29.378872916666669</v>
       </c>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A420" s="4">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A420">
         <v>29</v>
       </c>
-      <c r="B420" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C420" s="4">
-        <v>7</v>
-      </c>
-      <c r="D420" s="4">
+      <c r="B420">
+        <v>2018</v>
+      </c>
+      <c r="C420">
+        <v>7</v>
+      </c>
+      <c r="D420">
         <v>4</v>
       </c>
-      <c r="E420" s="8">
+      <c r="E420">
         <v>28.928956249999999</v>
       </c>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A421" s="4">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A421">
         <v>29</v>
       </c>
-      <c r="B421" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C421" s="4">
-        <v>7</v>
-      </c>
-      <c r="D421" s="4">
-        <v>5</v>
-      </c>
-      <c r="E421" s="8">
+      <c r="B421">
+        <v>2018</v>
+      </c>
+      <c r="C421">
+        <v>7</v>
+      </c>
+      <c r="D421">
+        <v>5</v>
+      </c>
+      <c r="E421">
         <v>28.744836956521741</v>
       </c>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A422" s="4">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A422">
         <v>29</v>
       </c>
-      <c r="B422" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C422" s="4">
-        <v>7</v>
-      </c>
-      <c r="D422" s="4">
-        <v>6</v>
-      </c>
-      <c r="E422" s="8">
+      <c r="B422">
+        <v>2018</v>
+      </c>
+      <c r="C422">
+        <v>7</v>
+      </c>
+      <c r="D422">
+        <v>6</v>
+      </c>
+      <c r="E422">
         <v>28.536372916666668</v>
       </c>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A423" s="4">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A423">
         <v>29</v>
       </c>
-      <c r="B423" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C423" s="4">
-        <v>7</v>
-      </c>
-      <c r="D423" s="4">
-        <v>7</v>
-      </c>
-      <c r="E423" s="8">
+      <c r="B423">
+        <v>2018</v>
+      </c>
+      <c r="C423">
+        <v>7</v>
+      </c>
+      <c r="D423">
+        <v>7</v>
+      </c>
+      <c r="E423">
         <v>28.116564583333329</v>
       </c>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A424" s="4">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A424">
         <v>29</v>
       </c>
-      <c r="B424" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C424" s="4">
-        <v>7</v>
-      </c>
-      <c r="D424" s="4">
+      <c r="B424">
+        <v>2018</v>
+      </c>
+      <c r="C424">
+        <v>7</v>
+      </c>
+      <c r="D424">
         <v>8</v>
       </c>
-      <c r="E424" s="8">
+      <c r="E424">
         <v>27.666866666666674</v>
       </c>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A425" s="4">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A425">
         <v>29</v>
       </c>
-      <c r="B425" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C425" s="4">
-        <v>7</v>
-      </c>
-      <c r="D425" s="4">
+      <c r="B425">
+        <v>2018</v>
+      </c>
+      <c r="C425">
+        <v>7</v>
+      </c>
+      <c r="D425">
         <v>9</v>
       </c>
-      <c r="E425" s="8">
+      <c r="E425">
         <v>27.194014583333331</v>
       </c>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A426" s="4">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A426">
         <v>29</v>
       </c>
-      <c r="B426" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C426" s="4">
-        <v>7</v>
-      </c>
-      <c r="D426" s="4">
+      <c r="B426">
+        <v>2018</v>
+      </c>
+      <c r="C426">
+        <v>7</v>
+      </c>
+      <c r="D426">
         <v>10</v>
       </c>
-      <c r="E426" s="8">
+      <c r="E426">
         <v>26.823718750000001</v>
       </c>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A427" s="4">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A427">
         <v>29</v>
       </c>
-      <c r="B427" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C427" s="4">
-        <v>7</v>
-      </c>
-      <c r="D427" s="4">
+      <c r="B427">
+        <v>2018</v>
+      </c>
+      <c r="C427">
+        <v>7</v>
+      </c>
+      <c r="D427">
         <v>11</v>
       </c>
-      <c r="E427" s="8">
+      <c r="E427">
         <v>26.598405555555559</v>
       </c>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A428" s="4">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A428">
         <v>29</v>
       </c>
-      <c r="B428" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C428" s="4">
-        <v>7</v>
-      </c>
-      <c r="D428" s="4">
+      <c r="B428">
+        <v>2018</v>
+      </c>
+      <c r="C428">
+        <v>7</v>
+      </c>
+      <c r="D428">
         <v>12</v>
       </c>
-      <c r="E428" s="8">
+      <c r="E428">
         <v>26.488768750000002</v>
       </c>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A429" s="4">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A429">
         <v>29</v>
       </c>
-      <c r="B429" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C429" s="4">
-        <v>7</v>
-      </c>
-      <c r="D429" s="4">
+      <c r="B429">
+        <v>2018</v>
+      </c>
+      <c r="C429">
+        <v>7</v>
+      </c>
+      <c r="D429">
         <v>13</v>
       </c>
-      <c r="E429" s="8">
+      <c r="E429">
         <v>26.512947916666665</v>
       </c>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A430" s="4">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A430">
         <v>29</v>
       </c>
-      <c r="B430" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C430" s="4">
-        <v>7</v>
-      </c>
-      <c r="D430" s="4">
+      <c r="B430">
+        <v>2018</v>
+      </c>
+      <c r="C430">
+        <v>7</v>
+      </c>
+      <c r="D430">
         <v>14</v>
       </c>
-      <c r="E430" s="8">
+      <c r="E430">
         <v>26.446662499999999</v>
       </c>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A431" s="4">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A431">
         <v>29</v>
       </c>
-      <c r="B431" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C431" s="4">
-        <v>7</v>
-      </c>
-      <c r="D431" s="4">
+      <c r="B431">
+        <v>2018</v>
+      </c>
+      <c r="C431">
+        <v>7</v>
+      </c>
+      <c r="D431">
         <v>15</v>
       </c>
-      <c r="E431" s="8">
+      <c r="E431">
         <v>26.306608333333333</v>
       </c>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A432" s="4">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A432">
         <v>29</v>
       </c>
-      <c r="B432" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C432" s="4">
-        <v>7</v>
-      </c>
-      <c r="D432" s="4">
+      <c r="B432">
+        <v>2018</v>
+      </c>
+      <c r="C432">
+        <v>7</v>
+      </c>
+      <c r="D432">
         <v>16</v>
       </c>
-      <c r="E432" s="8">
+      <c r="E432">
         <v>26.141222499999998</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A433" s="4">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A433">
         <v>29</v>
       </c>
-      <c r="B433" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C433" s="4">
-        <v>7</v>
-      </c>
-      <c r="D433" s="4">
+      <c r="B433">
+        <v>2018</v>
+      </c>
+      <c r="C433">
+        <v>7</v>
+      </c>
+      <c r="D433">
         <v>17</v>
       </c>
-      <c r="E433" s="8">
+      <c r="E433">
         <v>25.785920833333336</v>
       </c>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A434" s="4">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A434">
         <v>29</v>
       </c>
-      <c r="B434" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C434" s="4">
-        <v>7</v>
-      </c>
-      <c r="D434" s="4">
+      <c r="B434">
+        <v>2018</v>
+      </c>
+      <c r="C434">
+        <v>7</v>
+      </c>
+      <c r="D434">
         <v>18</v>
       </c>
-      <c r="E434" s="8">
+      <c r="E434">
         <v>25.383822916666663</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A435" s="4">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A435">
         <v>29</v>
       </c>
-      <c r="B435" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C435" s="4">
-        <v>7</v>
-      </c>
-      <c r="D435" s="4">
+      <c r="B435">
+        <v>2018</v>
+      </c>
+      <c r="C435">
+        <v>7</v>
+      </c>
+      <c r="D435">
         <v>19</v>
       </c>
-      <c r="E435" s="8">
+      <c r="E435">
         <v>25.217963157894733</v>
       </c>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A436" s="4">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A436">
         <v>29</v>
       </c>
-      <c r="B436" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C436" s="4">
-        <v>7</v>
-      </c>
-      <c r="D436" s="4">
+      <c r="B436">
+        <v>2018</v>
+      </c>
+      <c r="C436">
+        <v>7</v>
+      </c>
+      <c r="D436">
         <v>20</v>
       </c>
-      <c r="E436" s="8">
+      <c r="E436">
         <v>25.157114583333339</v>
       </c>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A437" s="4">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A437">
         <v>29</v>
       </c>
-      <c r="B437" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C437" s="4">
-        <v>7</v>
-      </c>
-      <c r="D437" s="4">
+      <c r="B437">
+        <v>2018</v>
+      </c>
+      <c r="C437">
+        <v>7</v>
+      </c>
+      <c r="D437">
         <v>21</v>
       </c>
-      <c r="E437" s="8">
+      <c r="E437">
         <v>25.159252083333339</v>
       </c>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A438" s="4">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A438">
         <v>29</v>
       </c>
-      <c r="B438" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C438" s="4">
-        <v>7</v>
-      </c>
-      <c r="D438" s="4">
+      <c r="B438">
+        <v>2018</v>
+      </c>
+      <c r="C438">
+        <v>7</v>
+      </c>
+      <c r="D438">
         <v>22</v>
       </c>
-      <c r="E438" s="8">
+      <c r="E438">
         <v>25.167777083333334</v>
       </c>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A439" s="4">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A439">
         <v>29</v>
       </c>
-      <c r="B439" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C439" s="4">
-        <v>7</v>
-      </c>
-      <c r="D439" s="4">
+      <c r="B439">
+        <v>2018</v>
+      </c>
+      <c r="C439">
+        <v>7</v>
+      </c>
+      <c r="D439">
         <v>23</v>
       </c>
-      <c r="E439" s="8">
+      <c r="E439">
         <v>25.159293478260871</v>
       </c>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A440" s="4">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A440">
         <v>29</v>
       </c>
-      <c r="B440" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C440" s="4">
-        <v>7</v>
-      </c>
-      <c r="D440" s="4">
+      <c r="B440">
+        <v>2018</v>
+      </c>
+      <c r="C440">
+        <v>7</v>
+      </c>
+      <c r="D440">
         <v>24</v>
       </c>
-      <c r="E440" s="8">
+      <c r="E440">
         <v>24.671093749999997</v>
       </c>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A441" s="4">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A441">
         <v>29</v>
       </c>
-      <c r="B441" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C441" s="4">
-        <v>7</v>
-      </c>
-      <c r="D441" s="4">
+      <c r="B441">
+        <v>2018</v>
+      </c>
+      <c r="C441">
+        <v>7</v>
+      </c>
+      <c r="D441">
         <v>25</v>
       </c>
-      <c r="E441" s="8">
+      <c r="E441">
         <v>24.390345833333338</v>
       </c>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A442" s="4">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A442">
         <v>29</v>
       </c>
-      <c r="B442" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C442" s="4">
-        <v>7</v>
-      </c>
-      <c r="D442" s="4">
+      <c r="B442">
+        <v>2018</v>
+      </c>
+      <c r="C442">
+        <v>7</v>
+      </c>
+      <c r="D442">
         <v>26</v>
       </c>
-      <c r="E442" s="8">
+      <c r="E442">
         <v>24.298504166666664</v>
       </c>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A443" s="4">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A443">
         <v>29</v>
       </c>
-      <c r="B443" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C443" s="4">
-        <v>7</v>
-      </c>
-      <c r="D443" s="4">
-        <v>27</v>
-      </c>
-      <c r="E443" s="8">
+      <c r="B443">
+        <v>2018</v>
+      </c>
+      <c r="C443">
+        <v>7</v>
+      </c>
+      <c r="D443">
+        <v>27</v>
+      </c>
+      <c r="E443">
         <v>24.33663125</v>
       </c>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A444" s="4">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A444">
         <v>29</v>
       </c>
-      <c r="B444" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C444" s="4">
-        <v>7</v>
-      </c>
-      <c r="D444" s="4">
-        <v>28</v>
-      </c>
-      <c r="E444" s="8">
+      <c r="B444">
+        <v>2018</v>
+      </c>
+      <c r="C444">
+        <v>7</v>
+      </c>
+      <c r="D444">
+        <v>28</v>
+      </c>
+      <c r="E444">
         <v>24.409877083333328</v>
       </c>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A445" s="4">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A445">
         <v>29</v>
       </c>
-      <c r="B445" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C445" s="4">
-        <v>7</v>
-      </c>
-      <c r="D445" s="4">
+      <c r="B445">
+        <v>2018</v>
+      </c>
+      <c r="C445">
+        <v>7</v>
+      </c>
+      <c r="D445">
         <v>29</v>
       </c>
-      <c r="E445" s="8">
+      <c r="E445">
         <v>24.529449999999997</v>
       </c>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A446" s="4">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A446">
         <v>29</v>
       </c>
-      <c r="B446" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C446" s="4">
-        <v>7</v>
-      </c>
-      <c r="D446" s="4">
+      <c r="B446">
+        <v>2018</v>
+      </c>
+      <c r="C446">
+        <v>7</v>
+      </c>
+      <c r="D446">
         <v>30</v>
       </c>
-      <c r="E446" s="8">
+      <c r="E446">
         <v>24.511927083333337</v>
       </c>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A447" s="4">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A447">
         <v>29</v>
       </c>
-      <c r="B447" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C447" s="4">
-        <v>7</v>
-      </c>
-      <c r="D447" s="4">
+      <c r="B447">
+        <v>2018</v>
+      </c>
+      <c r="C447">
+        <v>7</v>
+      </c>
+      <c r="D447">
         <v>31</v>
       </c>
-      <c r="E447" s="8">
+      <c r="E447">
         <v>24.478690909090911</v>
       </c>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A448" s="4">
+    <row r="448" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A448">
         <v>29</v>
       </c>
-      <c r="B448" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C448" s="4">
+      <c r="B448">
+        <v>2018</v>
+      </c>
+      <c r="C448">
         <v>8</v>
       </c>
-      <c r="D448" s="4">
+      <c r="D448">
         <v>1</v>
       </c>
-      <c r="E448" s="9">
+      <c r="E448">
         <v>24.439062500000002</v>
       </c>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A449" s="4">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A449">
         <v>29</v>
       </c>
-      <c r="B449" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C449" s="4">
+      <c r="B449">
+        <v>2018</v>
+      </c>
+      <c r="C449">
         <v>8</v>
       </c>
-      <c r="D449" s="4">
+      <c r="D449">
         <v>2</v>
       </c>
-      <c r="E449" s="9">
+      <c r="E449">
         <v>24.387152083333334</v>
       </c>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A450" s="4">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A450">
         <v>29</v>
       </c>
-      <c r="B450" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C450" s="4">
+      <c r="B450">
+        <v>2018</v>
+      </c>
+      <c r="C450">
         <v>8</v>
       </c>
-      <c r="D450" s="4">
+      <c r="D450">
         <v>3</v>
       </c>
-      <c r="E450" s="9">
+      <c r="E450">
         <v>24.336649999999995</v>
       </c>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A451" s="4">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A451">
         <v>29</v>
       </c>
-      <c r="B451" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C451" s="4">
+      <c r="B451">
+        <v>2018</v>
+      </c>
+      <c r="C451">
         <v>8</v>
       </c>
-      <c r="D451" s="4">
+      <c r="D451">
         <v>4</v>
       </c>
-      <c r="E451" s="9">
+      <c r="E451">
         <v>24.247795833333331</v>
       </c>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A452" s="4">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A452">
         <v>29</v>
       </c>
-      <c r="B452" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C452" s="4">
+      <c r="B452">
+        <v>2018</v>
+      </c>
+      <c r="C452">
         <v>8</v>
       </c>
-      <c r="D452" s="4">
-        <v>5</v>
-      </c>
-      <c r="E452" s="9">
+      <c r="D452">
+        <v>5</v>
+      </c>
+      <c r="E452">
         <v>24.150681818181816</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8618,7 +10819,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
